--- a/primary_survey/v2025/conf/nvi_answer_key_20260316.xlsx
+++ b/primary_survey/v2025/conf/nvi_answer_key_20260316.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mike\Desktop\2_responsibilities\nvi_etl\primary_survey\v2025\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84C2AB7-43BB-4A91-8C2E-3F473B6EC240}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8E1234-108A-4336-985C-E890CC27B9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="3220" windowWidth="19200" windowHeight="11710" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="25760" windowHeight="16160" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
@@ -3307,28 +3307,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:T730"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25.453125" style="3" customWidth="1"/>
+    <col min="1" max="2" width="25.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="29" style="3" customWidth="1"/>
-    <col min="4" max="5" width="34.1796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="52.1796875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="51.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="25.453125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.453125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="25.453125" style="3" customWidth="1"/>
+    <col min="4" max="5" width="34.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="52.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="51.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="25.42578125" style="3" customWidth="1"/>
     <col min="14" max="14" width="118" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.453125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="43.81640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="35.81640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="25.453125" style="3" customWidth="1"/>
-    <col min="19" max="20" width="25.453125" style="11" customWidth="1"/>
-    <col min="21" max="16384" width="8.7265625" style="1"/>
+    <col min="15" max="15" width="25.42578125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="43.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="25.42578125" style="3" customWidth="1"/>
+    <col min="19" max="20" width="25.42578125" style="11" customWidth="1"/>
+    <col min="21" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>512</v>
       </c>
@@ -3390,7 +3390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -3630,7 +3630,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -3990,7 +3990,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2</v>
       </c>
@@ -4110,7 +4110,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -4170,7 +4170,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -4230,7 +4230,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>3</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>3</v>
       </c>
@@ -4470,7 +4470,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -4530,7 +4530,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>3</v>
       </c>
@@ -4590,7 +4590,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -4650,7 +4650,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>3</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>3</v>
       </c>
@@ -4770,7 +4770,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>3</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>3</v>
       </c>
@@ -4890,7 +4890,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>3</v>
       </c>
@@ -4950,7 +4950,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>3</v>
       </c>
@@ -5010,7 +5010,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>3</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>3</v>
       </c>
@@ -5130,7 +5130,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>3</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>3</v>
       </c>
@@ -5250,7 +5250,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>3</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>3</v>
       </c>
@@ -5370,7 +5370,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -5430,7 +5430,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>3</v>
       </c>
@@ -5490,7 +5490,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>3</v>
       </c>
@@ -5550,7 +5550,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>3</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>3</v>
       </c>
@@ -5670,7 +5670,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>3</v>
       </c>
@@ -5730,7 +5730,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>3</v>
       </c>
@@ -5790,7 +5790,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>3</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>3</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>3</v>
       </c>
@@ -6030,7 +6030,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>5</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>5</v>
       </c>
@@ -6150,7 +6150,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>5</v>
       </c>
@@ -6210,7 +6210,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="49" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>5</v>
       </c>
@@ -6270,7 +6270,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="50" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>6</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>6</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="52" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>6</v>
       </c>
@@ -6438,7 +6438,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="53" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>6</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>6</v>
       </c>
@@ -6550,7 +6550,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="55" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>6</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>6</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>9</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="58" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>9</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>9</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="60" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>9</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>9</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="62" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>16</v>
       </c>
@@ -6998,7 +6998,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="63" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>16</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="64" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>18</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="65" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>18</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="66" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>18</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="67" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>18</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="68" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>19</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="69" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>19</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="70" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>19</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="71" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>20</v>
       </c>
@@ -7530,7 +7530,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="72" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>20</v>
       </c>
@@ -7586,7 +7586,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="73" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>20</v>
       </c>
@@ -7642,7 +7642,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="74" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>20</v>
       </c>
@@ -7698,7 +7698,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="75" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>20</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="76" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>22</v>
       </c>
@@ -7814,7 +7814,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="77" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>22</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="78" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>22</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="79" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>22</v>
       </c>
@@ -7994,7 +7994,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="80" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>22</v>
       </c>
@@ -8054,7 +8054,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="81" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>23</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>23</v>
       </c>
@@ -8174,7 +8174,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>23</v>
       </c>
@@ -8234,7 +8234,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>23</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>23</v>
       </c>
@@ -8354,7 +8354,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>23</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>25</v>
       </c>
@@ -8474,7 +8474,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>25</v>
       </c>
@@ -8534,7 +8534,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="89" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>25</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="90" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>25</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="91" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>25</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="92" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>25</v>
       </c>
@@ -8774,7 +8774,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>26</v>
       </c>
@@ -8834,7 +8834,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="94" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>26</v>
       </c>
@@ -8894,7 +8894,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="95" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>26</v>
       </c>
@@ -8954,7 +8954,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="96" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>26</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="97" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>26</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="98" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>26</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="99" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>27</v>
       </c>
@@ -9194,7 +9194,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>27</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>27</v>
       </c>
@@ -9314,7 +9314,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>27</v>
       </c>
@@ -9374,7 +9374,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="104" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>27</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="105" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>29</v>
       </c>
@@ -9554,7 +9554,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>29</v>
       </c>
@@ -9614,7 +9614,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>29</v>
       </c>
@@ -9674,7 +9674,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>29</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="109" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>29</v>
       </c>
@@ -9794,7 +9794,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>33</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>33</v>
       </c>
@@ -9914,7 +9914,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>33</v>
       </c>
@@ -9974,7 +9974,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="113" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>33</v>
       </c>
@@ -10034,7 +10034,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="114" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>33</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="115" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>33</v>
       </c>
@@ -10154,7 +10154,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="116" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>33</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="117" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>33</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="118" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>33</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="119" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>33</v>
       </c>
@@ -10394,7 +10394,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="120" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>33</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="121" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>33</v>
       </c>
@@ -10514,7 +10514,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>33</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>33</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>33</v>
       </c>
@@ -10694,7 +10694,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>33</v>
       </c>
@@ -10754,7 +10754,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>33</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>33</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>33</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>33</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>33</v>
       </c>
@@ -11054,7 +11054,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>33</v>
       </c>
@@ -11114,7 +11114,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>33</v>
       </c>
@@ -11174,7 +11174,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="133" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>33</v>
       </c>
@@ -11234,7 +11234,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>34</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>34</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>34</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>34</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>34</v>
       </c>
@@ -11534,7 +11534,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>34</v>
       </c>
@@ -11594,7 +11594,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>35</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>35</v>
       </c>
@@ -11714,7 +11714,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>35</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="143" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>35</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="144" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>35</v>
       </c>
@@ -11894,7 +11894,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="145" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>35</v>
       </c>
@@ -11954,7 +11954,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="146" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>36</v>
       </c>
@@ -12014,7 +12014,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="147" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>36</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="148" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>36</v>
       </c>
@@ -12134,7 +12134,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="149" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>36</v>
       </c>
@@ -12194,7 +12194,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="150" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>36</v>
       </c>
@@ -12254,7 +12254,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="151" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>36</v>
       </c>
@@ -12314,7 +12314,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="152" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>37</v>
       </c>
@@ -12374,7 +12374,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="153" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>37</v>
       </c>
@@ -12434,7 +12434,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="154" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>37</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="155" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>37</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="156" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>37</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="157" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>37</v>
       </c>
@@ -12674,7 +12674,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="158" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>37</v>
       </c>
@@ -12734,7 +12734,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="159" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>37</v>
       </c>
@@ -12794,7 +12794,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="160" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>37</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="161" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>37</v>
       </c>
@@ -12914,7 +12914,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="162" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>38</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="163" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>38</v>
       </c>
@@ -13034,7 +13034,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="164" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>38</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="165" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>38</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="166" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>38</v>
       </c>
@@ -13214,7 +13214,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="167" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>39</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="168" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>39</v>
       </c>
@@ -13326,7 +13326,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="169" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>39</v>
       </c>
@@ -13382,7 +13382,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="170" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>39</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="171" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>39</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="172" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>40</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="173" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>40</v>
       </c>
@@ -13614,7 +13614,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="174" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>40</v>
       </c>
@@ -13674,7 +13674,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="175" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>40</v>
       </c>
@@ -13734,7 +13734,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="176" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>40</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="177" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>41</v>
       </c>
@@ -13854,7 +13854,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="178" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>41</v>
       </c>
@@ -13914,7 +13914,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="179" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>41</v>
       </c>
@@ -13974,7 +13974,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="180" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>41</v>
       </c>
@@ -14034,7 +14034,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="181" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>41</v>
       </c>
@@ -14094,7 +14094,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="182" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>42</v>
       </c>
@@ -14154,7 +14154,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="183" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>42</v>
       </c>
@@ -14214,7 +14214,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="184" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>42</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="185" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>42</v>
       </c>
@@ -14334,7 +14334,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="186" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>42</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="187" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>43</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="188" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>43</v>
       </c>
@@ -14514,7 +14514,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="189" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>43</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="190" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>43</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="191" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>44</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="192" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>44</v>
       </c>
@@ -14746,7 +14746,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="193" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>44</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="194" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>44</v>
       </c>
@@ -14858,7 +14858,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="195" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>44</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="196" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>45</v>
       </c>
@@ -14974,7 +14974,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="197" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>45</v>
       </c>
@@ -15034,7 +15034,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="198" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>45</v>
       </c>
@@ -15094,7 +15094,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="199" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>45</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="200" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>45</v>
       </c>
@@ -15214,7 +15214,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="201" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>45</v>
       </c>
@@ -15274,7 +15274,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="202" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>46</v>
       </c>
@@ -15334,7 +15334,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="203" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>46</v>
       </c>
@@ -15394,7 +15394,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="204" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>46</v>
       </c>
@@ -15454,7 +15454,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="205" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>47</v>
       </c>
@@ -15514,7 +15514,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="206" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>47</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="207" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>47</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="208" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>47</v>
       </c>
@@ -15694,7 +15694,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="209" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>47</v>
       </c>
@@ -15754,7 +15754,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="210" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>47</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="211" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>47</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="212" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>47</v>
       </c>
@@ -15934,7 +15934,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="213" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>47</v>
       </c>
@@ -15994,7 +15994,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="214" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>47</v>
       </c>
@@ -16054,7 +16054,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="215" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -16114,7 +16114,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="216" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>47</v>
       </c>
@@ -16174,7 +16174,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="217" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>47</v>
       </c>
@@ -16234,7 +16234,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="218" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>47</v>
       </c>
@@ -16294,7 +16294,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="219" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>47</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="220" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>47</v>
       </c>
@@ -16414,7 +16414,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="221" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>47</v>
       </c>
@@ -16474,7 +16474,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="222" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>47</v>
       </c>
@@ -16534,7 +16534,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="223" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>47</v>
       </c>
@@ -16594,7 +16594,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="224" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>47</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="225" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>47</v>
       </c>
@@ -16714,7 +16714,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="226" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>47</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="227" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>47</v>
       </c>
@@ -16834,7 +16834,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="228" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>47</v>
       </c>
@@ -16894,7 +16894,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="229" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>47</v>
       </c>
@@ -16954,7 +16954,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="230" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>47</v>
       </c>
@@ -17014,7 +17014,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="231" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>47</v>
       </c>
@@ -17074,7 +17074,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="232" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>47</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="233" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>47</v>
       </c>
@@ -17194,7 +17194,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="234" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>47</v>
       </c>
@@ -17254,7 +17254,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="235" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>47</v>
       </c>
@@ -17314,7 +17314,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="236" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>47</v>
       </c>
@@ -17374,7 +17374,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="237" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>47</v>
       </c>
@@ -17434,7 +17434,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="238" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>47</v>
       </c>
@@ -17494,7 +17494,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="239" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>47</v>
       </c>
@@ -17554,7 +17554,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="240" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>47</v>
       </c>
@@ -17614,7 +17614,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="241" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>47</v>
       </c>
@@ -17674,7 +17674,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="242" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>47</v>
       </c>
@@ -17734,7 +17734,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="243" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>47</v>
       </c>
@@ -17794,7 +17794,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="244" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>47</v>
       </c>
@@ -17854,7 +17854,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="245" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>47</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="246" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>47</v>
       </c>
@@ -17974,7 +17974,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="247" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>47</v>
       </c>
@@ -18034,7 +18034,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="248" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>47</v>
       </c>
@@ -18094,7 +18094,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="249" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>47</v>
       </c>
@@ -18154,7 +18154,7 @@
         <v>73050</v>
       </c>
     </row>
-    <row r="250" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>48</v>
       </c>
@@ -18208,7 +18208,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="251" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>48</v>
       </c>
@@ -18262,7 +18262,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="252" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>48</v>
       </c>
@@ -18316,7 +18316,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="253" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>48</v>
       </c>
@@ -18370,7 +18370,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="254" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>48</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="255" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>48</v>
       </c>
@@ -18478,7 +18478,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="256" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>49</v>
       </c>
@@ -18534,7 +18534,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="257" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>49</v>
       </c>
@@ -18590,7 +18590,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="258" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>49</v>
       </c>
@@ -18646,7 +18646,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="259" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>49</v>
       </c>
@@ -18702,7 +18702,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="260" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>49</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="261" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>50</v>
       </c>
@@ -18814,7 +18814,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="262" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>50</v>
       </c>
@@ -18870,7 +18870,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="263" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
         <v>50</v>
       </c>
@@ -18926,7 +18926,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="264" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>50</v>
       </c>
@@ -18982,7 +18982,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="265" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
         <v>51</v>
       </c>
@@ -19038,7 +19038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="266" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>51</v>
       </c>
@@ -19094,7 +19094,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="267" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>51</v>
       </c>
@@ -19150,7 +19150,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="268" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>51</v>
       </c>
@@ -19206,7 +19206,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="269" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>52</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="270" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>52</v>
       </c>
@@ -19318,7 +19318,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="271" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>52</v>
       </c>
@@ -19374,7 +19374,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="272" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>52</v>
       </c>
@@ -19430,7 +19430,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="273" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>52</v>
       </c>
@@ -19486,7 +19486,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="274" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>53</v>
       </c>
@@ -19546,7 +19546,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="275" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>53</v>
       </c>
@@ -19606,7 +19606,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="276" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>53</v>
       </c>
@@ -19666,7 +19666,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="277" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>54</v>
       </c>
@@ -19726,7 +19726,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="278" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>54</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="279" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>54</v>
       </c>
@@ -19846,7 +19846,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="280" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>54</v>
       </c>
@@ -19906,7 +19906,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="281" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>54</v>
       </c>
@@ -19966,7 +19966,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="282" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>54</v>
       </c>
@@ -20026,7 +20026,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="283" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>55</v>
       </c>
@@ -20086,7 +20086,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="284" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>55</v>
       </c>
@@ -20146,7 +20146,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="285" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>55</v>
       </c>
@@ -20206,7 +20206,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="286" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>56</v>
       </c>
@@ -20262,7 +20262,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="287" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>56</v>
       </c>
@@ -20318,7 +20318,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="288" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>56</v>
       </c>
@@ -20374,7 +20374,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="289" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>56</v>
       </c>
@@ -20430,7 +20430,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="290" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>56</v>
       </c>
@@ -20486,7 +20486,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="291" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>56</v>
       </c>
@@ -20542,7 +20542,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="292" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>56</v>
       </c>
@@ -20598,7 +20598,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="293" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>56</v>
       </c>
@@ -20654,7 +20654,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="294" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>57</v>
       </c>
@@ -20710,7 +20710,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="295" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>57</v>
       </c>
@@ -20766,7 +20766,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="296" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>57</v>
       </c>
@@ -20822,7 +20822,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="297" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>57</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="298" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>57</v>
       </c>
@@ -20934,7 +20934,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="299" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>57</v>
       </c>
@@ -20990,7 +20990,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="300" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>57</v>
       </c>
@@ -21046,7 +21046,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="301" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>57</v>
       </c>
@@ -21102,7 +21102,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="302" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>58</v>
       </c>
@@ -21158,7 +21158,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="303" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>58</v>
       </c>
@@ -21214,7 +21214,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="304" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>62</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="305" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>62</v>
       </c>
@@ -21326,7 +21326,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="306" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>59</v>
       </c>
@@ -21386,7 +21386,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="307" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>59</v>
       </c>
@@ -21446,7 +21446,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="308" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>59</v>
       </c>
@@ -21506,7 +21506,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="309" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>59</v>
       </c>
@@ -21566,7 +21566,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="310" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>59</v>
       </c>
@@ -21626,7 +21626,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="311" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>60</v>
       </c>
@@ -21686,7 +21686,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="312" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>60</v>
       </c>
@@ -21746,7 +21746,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="313" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>60</v>
       </c>
@@ -21806,7 +21806,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="314" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>60</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="315" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>60</v>
       </c>
@@ -21926,7 +21926,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="316" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>61</v>
       </c>
@@ -21982,7 +21982,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="317" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>61</v>
       </c>
@@ -22038,7 +22038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="318" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>61</v>
       </c>
@@ -22094,7 +22094,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="319" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>61</v>
       </c>
@@ -22150,7 +22150,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="320" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>61</v>
       </c>
@@ -22206,7 +22206,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="321" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>61</v>
       </c>
@@ -22262,7 +22262,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="322" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>62</v>
       </c>
@@ -22322,7 +22322,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="323" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>62</v>
       </c>
@@ -22382,7 +22382,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="324" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>64</v>
       </c>
@@ -22436,7 +22436,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="325" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>64</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="326" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>64</v>
       </c>
@@ -22544,7 +22544,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="327" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>64</v>
       </c>
@@ -22598,7 +22598,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="328" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>64</v>
       </c>
@@ -22652,7 +22652,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="329" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>89</v>
       </c>
@@ -22712,7 +22712,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="330" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>89</v>
       </c>
@@ -22772,7 +22772,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="331" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>89</v>
       </c>
@@ -22832,7 +22832,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="332" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>90</v>
       </c>
@@ -22892,7 +22892,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="333" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>90</v>
       </c>
@@ -22952,7 +22952,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="334" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>90</v>
       </c>
@@ -23012,7 +23012,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="335" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>88</v>
       </c>
@@ -23072,7 +23072,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="336" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>88</v>
       </c>
@@ -23132,7 +23132,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="337" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>88</v>
       </c>
@@ -23190,7 +23190,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="338" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="b">
         <v>0</v>
@@ -23244,7 +23244,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="339" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="b">
         <v>0</v>
@@ -23298,7 +23298,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="340" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="b">
         <v>0</v>
@@ -23352,7 +23352,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="341" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="b">
         <v>0</v>
@@ -23406,7 +23406,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="342" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="b">
         <v>0</v>
@@ -23460,7 +23460,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="343" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="b">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="344" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="b">
         <v>0</v>
@@ -23568,7 +23568,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="345" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>82</v>
       </c>
@@ -23628,7 +23628,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="346" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>82</v>
       </c>
@@ -23688,7 +23688,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="347" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>82</v>
       </c>
@@ -23748,7 +23748,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="348" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>82</v>
       </c>
@@ -23808,7 +23808,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="349" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>82</v>
       </c>
@@ -23868,7 +23868,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="350" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>82</v>
       </c>
@@ -23928,7 +23928,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="351" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>81</v>
       </c>
@@ -23988,7 +23988,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="352" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>81</v>
       </c>
@@ -24048,7 +24048,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="353" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>81</v>
       </c>
@@ -24108,7 +24108,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="354" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>81</v>
       </c>
@@ -24168,7 +24168,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="355" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>81</v>
       </c>
@@ -24228,7 +24228,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="356" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>81</v>
       </c>
@@ -24288,7 +24288,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="357" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>76</v>
       </c>
@@ -24348,7 +24348,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="358" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>76</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="359" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>76</v>
       </c>
@@ -24468,7 +24468,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="360" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>76</v>
       </c>
@@ -24528,7 +24528,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="361" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>75</v>
       </c>
@@ -24588,7 +24588,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="362" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>75</v>
       </c>
@@ -24648,7 +24648,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="363" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>75</v>
       </c>
@@ -24708,7 +24708,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="364" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>75</v>
       </c>
@@ -24768,7 +24768,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="365" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>74</v>
       </c>
@@ -24824,7 +24824,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="366" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>74</v>
       </c>
@@ -24880,7 +24880,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="367" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>74</v>
       </c>
@@ -24936,7 +24936,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="368" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>74</v>
       </c>
@@ -24992,7 +24992,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="369" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>74</v>
       </c>
@@ -25048,7 +25048,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="370" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>87</v>
       </c>
@@ -25108,7 +25108,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="371" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>87</v>
       </c>
@@ -25168,7 +25168,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="372" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>94</v>
       </c>
@@ -25224,7 +25224,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="373" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>94</v>
       </c>
@@ -25280,7 +25280,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="374" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>94</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="375" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>94</v>
       </c>
@@ -25392,7 +25392,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="376" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>94</v>
       </c>
@@ -25448,7 +25448,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="377" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>94</v>
       </c>
@@ -25504,7 +25504,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="378" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>94</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="379" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>94</v>
       </c>
@@ -25616,7 +25616,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="380" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>94</v>
       </c>
@@ -25672,7 +25672,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="381" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>94</v>
       </c>
@@ -25728,7 +25728,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="382" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>94</v>
       </c>
@@ -25784,7 +25784,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="383" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>94</v>
       </c>
@@ -25840,7 +25840,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="384" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>94</v>
       </c>
@@ -25896,7 +25896,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="385" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A385" s="2"/>
       <c r="B385" s="2" t="b">
         <v>0</v>
@@ -25954,7 +25954,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="386" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A386" s="2"/>
       <c r="B386" s="2" t="b">
         <v>0</v>
@@ -26012,7 +26012,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="387" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A387" s="2"/>
       <c r="B387" s="2" t="b">
         <v>0</v>
@@ -26070,7 +26070,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="388" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A388" s="2"/>
       <c r="B388" s="2" t="b">
         <v>0</v>
@@ -26128,7 +26128,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="389" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A389" s="2"/>
       <c r="B389" s="2" t="b">
         <v>0</v>
@@ -26186,7 +26186,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="390" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
         <v>79</v>
       </c>
@@ -26246,7 +26246,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="391" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
         <v>79</v>
       </c>
@@ -26306,7 +26306,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="392" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
         <v>79</v>
       </c>
@@ -26366,7 +26366,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="393" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>79</v>
       </c>
@@ -26426,7 +26426,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="394" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>79</v>
       </c>
@@ -26486,7 +26486,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="395" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>78</v>
       </c>
@@ -26546,7 +26546,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="396" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>78</v>
       </c>
@@ -26606,7 +26606,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="397" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>78</v>
       </c>
@@ -26666,7 +26666,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="398" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>78</v>
       </c>
@@ -26726,7 +26726,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="399" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>78</v>
       </c>
@@ -26786,7 +26786,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="400" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A400" s="2"/>
       <c r="B400" s="2" t="b">
         <v>0</v>
@@ -26844,7 +26844,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="401" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A401" s="2"/>
       <c r="B401" s="2" t="b">
         <v>0</v>
@@ -26902,7 +26902,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="402" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A402" s="2"/>
       <c r="B402" s="2" t="b">
         <v>0</v>
@@ -26960,7 +26960,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="403" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A403" s="2"/>
       <c r="B403" s="2" t="b">
         <v>0</v>
@@ -27018,7 +27018,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="404" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A404" s="2"/>
       <c r="B404" s="2" t="b">
         <v>0</v>
@@ -27076,7 +27076,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="405" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A405" s="2"/>
       <c r="B405" s="2" t="b">
         <v>0</v>
@@ -27134,7 +27134,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="406" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A406" s="2"/>
       <c r="B406" s="2" t="b">
         <v>0</v>
@@ -27192,7 +27192,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="407" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="b">
         <v>0</v>
@@ -27250,7 +27250,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="408" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A408" s="2"/>
       <c r="B408" s="2" t="b">
         <v>0</v>
@@ -27308,7 +27308,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="409" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A409" s="2"/>
       <c r="B409" s="2" t="b">
         <v>0</v>
@@ -27366,7 +27366,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="410" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A410" s="2"/>
       <c r="B410" s="2" t="b">
         <v>0</v>
@@ -27424,7 +27424,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="411" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A411" s="2"/>
       <c r="B411" s="2" t="b">
         <v>0</v>
@@ -27482,7 +27482,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="412" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A412" s="2"/>
       <c r="B412" s="2" t="b">
         <v>0</v>
@@ -27540,7 +27540,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="413" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A413" s="2"/>
       <c r="B413" s="2" t="b">
         <v>0</v>
@@ -27598,7 +27598,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="414" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A414" s="2"/>
       <c r="B414" s="2" t="b">
         <v>0</v>
@@ -27656,7 +27656,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="415" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A415" s="2"/>
       <c r="B415" s="2" t="b">
         <v>0</v>
@@ -27714,7 +27714,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="416" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A416" s="2"/>
       <c r="B416" s="2" t="b">
         <v>0</v>
@@ -27772,7 +27772,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="417" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A417" s="2"/>
       <c r="B417" s="2" t="b">
         <v>0</v>
@@ -27830,7 +27830,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="418" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A418" s="2"/>
       <c r="B418" s="2" t="b">
         <v>0</v>
@@ -27888,7 +27888,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="419" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A419" s="2"/>
       <c r="B419" s="2" t="b">
         <v>0</v>
@@ -27946,7 +27946,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="420" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A420" s="2"/>
       <c r="B420" s="2" t="b">
         <v>0</v>
@@ -28004,7 +28004,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="421" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A421" s="2"/>
       <c r="B421" s="2" t="b">
         <v>0</v>
@@ -28062,7 +28062,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="422" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A422" s="2"/>
       <c r="B422" s="2" t="b">
         <v>0</v>
@@ -28120,7 +28120,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="423" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="b">
         <v>0</v>
@@ -28178,7 +28178,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="424" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A424" s="2"/>
       <c r="B424" s="2" t="b">
         <v>0</v>
@@ -28236,7 +28236,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="425" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A425" s="2"/>
       <c r="B425" s="2" t="b">
         <v>0</v>
@@ -28294,7 +28294,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="426" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A426" s="2"/>
       <c r="B426" s="2" t="b">
         <v>0</v>
@@ -28352,7 +28352,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="427" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A427" s="2"/>
       <c r="B427" s="2" t="b">
         <v>0</v>
@@ -28410,7 +28410,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="428" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A428" s="2"/>
       <c r="B428" s="2" t="b">
         <v>0</v>
@@ -28468,7 +28468,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="429" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A429" s="2"/>
       <c r="B429" s="2" t="b">
         <v>0</v>
@@ -28526,7 +28526,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="430" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A430" s="2"/>
       <c r="B430" s="2" t="b">
         <v>0</v>
@@ -28584,7 +28584,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="431" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A431" s="2"/>
       <c r="B431" s="2" t="b">
         <v>0</v>
@@ -28642,7 +28642,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="432" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A432" s="2"/>
       <c r="B432" s="2" t="b">
         <v>0</v>
@@ -28700,7 +28700,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="433" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A433" s="2"/>
       <c r="B433" s="2" t="b">
         <v>0</v>
@@ -28758,7 +28758,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="434" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A434" s="2"/>
       <c r="B434" s="2" t="b">
         <v>0</v>
@@ -28816,7 +28816,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="435" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A435" s="2"/>
       <c r="B435" s="2" t="b">
         <v>0</v>
@@ -28874,7 +28874,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="436" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A436" s="2"/>
       <c r="B436" s="2" t="b">
         <v>0</v>
@@ -28932,7 +28932,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="437" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A437" s="2"/>
       <c r="B437" s="2" t="b">
         <v>0</v>
@@ -28990,7 +28990,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="438" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A438" s="2"/>
       <c r="B438" s="2" t="b">
         <v>0</v>
@@ -29048,7 +29048,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="439" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="b">
         <v>0</v>
@@ -29106,7 +29106,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="440" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A440" s="2"/>
       <c r="B440" s="2" t="b">
         <v>0</v>
@@ -29164,7 +29164,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="441" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A441" s="2"/>
       <c r="B441" s="2" t="b">
         <v>0</v>
@@ -29222,7 +29222,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="442" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A442" s="2"/>
       <c r="B442" s="2" t="b">
         <v>0</v>
@@ -29280,7 +29280,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="443" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A443" s="2"/>
       <c r="B443" s="2" t="b">
         <v>0</v>
@@ -29338,7 +29338,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="444" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A444" s="2"/>
       <c r="B444" s="2" t="b">
         <v>0</v>
@@ -29396,7 +29396,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="445" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A445" s="2"/>
       <c r="B445" s="2" t="b">
         <v>0</v>
@@ -29454,7 +29454,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="446" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A446" s="2"/>
       <c r="B446" s="2" t="b">
         <v>0</v>
@@ -29512,7 +29512,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="447" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A447" s="2"/>
       <c r="B447" s="2" t="b">
         <v>0</v>
@@ -29570,7 +29570,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="448" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A448" s="2"/>
       <c r="B448" s="2" t="b">
         <v>0</v>
@@ -29628,7 +29628,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="449" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A449" s="2"/>
       <c r="B449" s="2" t="b">
         <v>0</v>
@@ -29686,7 +29686,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="450" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>
       <c r="B450" s="2" t="b">
         <v>0</v>
@@ -29744,7 +29744,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="451" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A451" s="2"/>
       <c r="B451" s="2" t="b">
         <v>0</v>
@@ -29802,7 +29802,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="452" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A452" s="2"/>
       <c r="B452" s="2" t="b">
         <v>0</v>
@@ -29860,7 +29860,7 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="453" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A453" s="2"/>
       <c r="B453" s="2" t="b">
         <v>0</v>
@@ -29914,7 +29914,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="454" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A454" s="2"/>
       <c r="B454" s="2" t="b">
         <v>0</v>
@@ -29968,7 +29968,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="455" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="b">
         <v>0</v>
@@ -30022,7 +30022,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="456" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A456" s="2"/>
       <c r="B456" s="2" t="b">
         <v>0</v>
@@ -30076,7 +30076,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="457" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A457" s="2"/>
       <c r="B457" s="2" t="b">
         <v>0</v>
@@ -30130,7 +30130,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="458" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A458" s="2"/>
       <c r="B458" s="2" t="b">
         <v>0</v>
@@ -30184,7 +30184,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="459" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A459" s="2"/>
       <c r="B459" s="2" t="b">
         <v>0</v>
@@ -30238,7 +30238,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="460" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A460" s="2"/>
       <c r="B460" s="2" t="b">
         <v>0</v>
@@ -30292,7 +30292,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="461" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A461" s="2"/>
       <c r="B461" s="2" t="b">
         <v>0</v>
@@ -30346,7 +30346,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="462" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A462" s="2"/>
       <c r="B462" s="2" t="b">
         <v>0</v>
@@ -30400,7 +30400,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="463" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A463" s="2"/>
       <c r="B463" s="2" t="b">
         <v>0</v>
@@ -30454,7 +30454,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="464" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A464" s="2"/>
       <c r="B464" s="2" t="b">
         <v>0</v>
@@ -30508,7 +30508,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="465" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A465" s="2"/>
       <c r="B465" s="2" t="b">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="466" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A466" s="2"/>
       <c r="B466" s="2" t="b">
         <v>0</v>
@@ -30616,7 +30616,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="467" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A467" s="2"/>
       <c r="B467" s="2" t="b">
         <v>0</v>
@@ -30670,7 +30670,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="468" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A468" s="2"/>
       <c r="B468" s="2" t="b">
         <v>0</v>
@@ -30724,7 +30724,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="469" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A469" s="2"/>
       <c r="B469" s="2" t="b">
         <v>0</v>
@@ -30778,7 +30778,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="470" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A470" s="2"/>
       <c r="B470" s="2" t="b">
         <v>0</v>
@@ -30832,7 +30832,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="471" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="b">
         <v>0</v>
@@ -30882,7 +30882,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="472" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A472" s="2"/>
       <c r="B472" s="2" t="b">
         <v>0</v>
@@ -30934,7 +30934,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="473" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A473" s="2"/>
       <c r="B473" s="2" t="b">
         <v>0</v>
@@ -30986,7 +30986,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="474" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A474" s="2"/>
       <c r="B474" s="2" t="b">
         <v>0</v>
@@ -31038,7 +31038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="475" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A475" s="2"/>
       <c r="B475" s="2" t="b">
         <v>0</v>
@@ -31090,7 +31090,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="476" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A476" s="2"/>
       <c r="B476" s="2" t="b">
         <v>0</v>
@@ -31142,7 +31142,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="477" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A477" s="2"/>
       <c r="B477" s="2" t="b">
         <v>0</v>
@@ -31194,7 +31194,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="478" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A478" s="2"/>
       <c r="B478" s="2" t="b">
         <v>0</v>
@@ -31244,7 +31244,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="479" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A479" s="2"/>
       <c r="B479" s="2" t="b">
         <v>0</v>
@@ -31296,7 +31296,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="480" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A480" s="2"/>
       <c r="B480" s="2" t="b">
         <v>0</v>
@@ -31348,7 +31348,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="481" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A481" s="2"/>
       <c r="B481" s="2" t="b">
         <v>0</v>
@@ -31400,7 +31400,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="482" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A482" s="2"/>
       <c r="B482" s="2" t="b">
         <v>0</v>
@@ -31452,7 +31452,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="483" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A483" s="2"/>
       <c r="B483" s="2" t="b">
         <v>0</v>
@@ -31504,7 +31504,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="484" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A484" s="2"/>
       <c r="B484" s="2" t="b">
         <v>0</v>
@@ -31556,7 +31556,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="485" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A485" s="2"/>
       <c r="B485" s="2" t="b">
         <v>0</v>
@@ -31608,7 +31608,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="486" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A486" s="2"/>
       <c r="B486" s="2" t="b">
         <v>0</v>
@@ -31662,7 +31662,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="487" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A487" s="2"/>
       <c r="B487" s="2" t="b">
         <v>0</v>
@@ -31716,7 +31716,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="488" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A488" s="2"/>
       <c r="B488" s="2" t="b">
         <v>0</v>
@@ -31770,7 +31770,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="489" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A489" s="2"/>
       <c r="B489" s="2" t="b">
         <v>0</v>
@@ -31824,7 +31824,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="490" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A490" s="2"/>
       <c r="B490" s="2" t="b">
         <v>0</v>
@@ -31878,7 +31878,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="491" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A491" s="2"/>
       <c r="B491" s="2" t="b">
         <v>0</v>
@@ -31932,7 +31932,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="492" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A492" s="2"/>
       <c r="B492" s="2" t="b">
         <v>0</v>
@@ -31986,7 +31986,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="493" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A493" s="2"/>
       <c r="B493" s="2" t="b">
         <v>0</v>
@@ -32040,7 +32040,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="494" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A494" s="2"/>
       <c r="B494" s="2" t="b">
         <v>0</v>
@@ -32094,7 +32094,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="495" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A495" s="2"/>
       <c r="B495" s="2" t="b">
         <v>0</v>
@@ -32148,7 +32148,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="496" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A496" s="2"/>
       <c r="B496" s="2" t="b">
         <v>0</v>
@@ -32202,7 +32202,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="497" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A497" s="2"/>
       <c r="B497" s="2" t="b">
         <v>0</v>
@@ -32256,7 +32256,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="498" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A498" s="2"/>
       <c r="B498" s="2" t="b">
         <v>0</v>
@@ -32310,7 +32310,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="499" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A499" s="2"/>
       <c r="B499" s="2" t="b">
         <v>0</v>
@@ -32364,7 +32364,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="500" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A500" s="2"/>
       <c r="B500" s="2" t="b">
         <v>0</v>
@@ -32418,7 +32418,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="501" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A501" s="2"/>
       <c r="B501" s="2" t="b">
         <v>0</v>
@@ -32472,7 +32472,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="502" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A502" s="2"/>
       <c r="B502" s="2" t="b">
         <v>0</v>
@@ -32530,7 +32530,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="503" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A503" s="2"/>
       <c r="B503" s="2" t="b">
         <v>0</v>
@@ -32588,7 +32588,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="504" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A504" s="2"/>
       <c r="B504" s="2" t="b">
         <v>0</v>
@@ -32646,7 +32646,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="505" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A505" s="2"/>
       <c r="B505" s="2" t="b">
         <v>0</v>
@@ -32704,7 +32704,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="506" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A506" s="2"/>
       <c r="B506" s="2" t="b">
         <v>0</v>
@@ -32762,7 +32762,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="507" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A507" s="2"/>
       <c r="B507" s="2" t="b">
         <v>0</v>
@@ -32820,7 +32820,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="508" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A508" s="2"/>
       <c r="B508" s="2" t="b">
         <v>0</v>
@@ -32878,7 +32878,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="509" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A509" s="2"/>
       <c r="B509" s="2" t="b">
         <v>0</v>
@@ -32936,7 +32936,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="510" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A510" s="2"/>
       <c r="B510" s="2" t="b">
         <v>0</v>
@@ -32994,7 +32994,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="511" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A511" s="2"/>
       <c r="B511" s="2" t="b">
         <v>0</v>
@@ -33052,7 +33052,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="512" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A512" s="2"/>
       <c r="B512" s="2" t="b">
         <v>0</v>
@@ -33110,7 +33110,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="513" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A513" s="2"/>
       <c r="B513" s="2" t="b">
         <v>0</v>
@@ -33168,7 +33168,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="514" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A514" s="2"/>
       <c r="B514" s="2" t="b">
         <v>0</v>
@@ -33226,7 +33226,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="515" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A515" s="2"/>
       <c r="B515" s="2" t="b">
         <v>0</v>
@@ -33284,7 +33284,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="516" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A516" s="2"/>
       <c r="B516" s="2" t="b">
         <v>0</v>
@@ -33342,7 +33342,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="517" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A517" s="2"/>
       <c r="B517" s="2" t="b">
         <v>0</v>
@@ -33400,7 +33400,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="518" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A518" s="2"/>
       <c r="B518" s="2" t="b">
         <v>0</v>
@@ -33458,7 +33458,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="519" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A519" s="2"/>
       <c r="B519" s="2" t="b">
         <v>0</v>
@@ -33516,7 +33516,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="520" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A520" s="2"/>
       <c r="B520" s="2" t="b">
         <v>0</v>
@@ -33574,7 +33574,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="521" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A521" s="2"/>
       <c r="B521" s="2" t="b">
         <v>0</v>
@@ -33632,7 +33632,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="522" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A522" s="2"/>
       <c r="B522" s="2" t="b">
         <v>0</v>
@@ -33690,7 +33690,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="523" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A523" s="2"/>
       <c r="B523" s="2" t="b">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="524" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A524" s="2"/>
       <c r="B524" s="2" t="b">
         <v>0</v>
@@ -33806,7 +33806,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="525" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A525" s="2"/>
       <c r="B525" s="2" t="b">
         <v>0</v>
@@ -33864,7 +33864,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="526" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A526" s="2"/>
       <c r="B526" s="2" t="b">
         <v>0</v>
@@ -33922,7 +33922,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="527" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A527" s="2"/>
       <c r="B527" s="2" t="b">
         <v>0</v>
@@ -33980,7 +33980,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="528" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A528" s="2"/>
       <c r="B528" s="2" t="b">
         <v>0</v>
@@ -34038,7 +34038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="529" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A529" s="2"/>
       <c r="B529" s="2" t="b">
         <v>0</v>
@@ -34096,7 +34096,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="530" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A530" s="2"/>
       <c r="B530" s="2" t="b">
         <v>0</v>
@@ -34154,7 +34154,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="531" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A531" s="2"/>
       <c r="B531" s="2" t="b">
         <v>0</v>
@@ -34212,7 +34212,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="532" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A532" s="2"/>
       <c r="B532" s="2" t="b">
         <v>0</v>
@@ -34270,7 +34270,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="533" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A533" s="2"/>
       <c r="B533" s="2" t="b">
         <v>0</v>
@@ -34328,7 +34328,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="534" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A534" s="2"/>
       <c r="B534" s="2" t="b">
         <v>0</v>
@@ -34386,7 +34386,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="535" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A535" s="2"/>
       <c r="B535" s="2" t="b">
         <v>0</v>
@@ -34444,7 +34444,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="536" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A536" s="2"/>
       <c r="B536" s="2" t="b">
         <v>0</v>
@@ -34502,7 +34502,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="537" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A537" s="2"/>
       <c r="B537" s="2" t="b">
         <v>0</v>
@@ -34560,7 +34560,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="538" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A538" s="2"/>
       <c r="B538" s="2" t="b">
         <v>0</v>
@@ -34618,7 +34618,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="539" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A539" s="2"/>
       <c r="B539" s="2" t="b">
         <v>0</v>
@@ -34676,7 +34676,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="540" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A540" s="2"/>
       <c r="B540" s="2" t="b">
         <v>0</v>
@@ -34734,7 +34734,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="541" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A541" s="2"/>
       <c r="B541" s="2" t="b">
         <v>0</v>
@@ -34792,7 +34792,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="542" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A542" s="2"/>
       <c r="B542" s="2" t="b">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="543" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A543" s="2"/>
       <c r="B543" s="2" t="b">
         <v>0</v>
@@ -34908,7 +34908,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="544" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A544" s="2"/>
       <c r="B544" s="2" t="b">
         <v>0</v>
@@ -34966,7 +34966,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="545" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A545" s="2"/>
       <c r="B545" s="2" t="b">
         <v>0</v>
@@ -35024,7 +35024,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="546" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A546" s="2"/>
       <c r="B546" s="2" t="b">
         <v>0</v>
@@ -35082,7 +35082,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="547" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A547" s="2"/>
       <c r="B547" s="2" t="b">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="548" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A548" s="2"/>
       <c r="B548" s="2" t="b">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="549" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A549" s="2"/>
       <c r="B549" s="2" t="b">
         <v>0</v>
@@ -35256,7 +35256,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="550" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A550" s="2"/>
       <c r="B550" s="2" t="b">
         <v>0</v>
@@ -35314,7 +35314,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="551" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A551" s="2"/>
       <c r="B551" s="2" t="b">
         <v>0</v>
@@ -35372,7 +35372,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="552" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A552" s="2"/>
       <c r="B552" s="2" t="b">
         <v>0</v>
@@ -35430,7 +35430,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="553" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A553" s="2"/>
       <c r="B553" s="2" t="b">
         <v>0</v>
@@ -35488,7 +35488,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="554" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A554" s="2"/>
       <c r="B554" s="2" t="b">
         <v>0</v>
@@ -35546,7 +35546,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="555" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A555" s="2"/>
       <c r="B555" s="2" t="b">
         <v>0</v>
@@ -35604,7 +35604,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="556" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A556" s="2"/>
       <c r="B556" s="2" t="b">
         <v>0</v>
@@ -35662,7 +35662,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="557" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A557" s="2"/>
       <c r="B557" s="2" t="b">
         <v>0</v>
@@ -35708,7 +35708,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="558" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A558" s="2"/>
       <c r="B558" s="2" t="b">
         <v>0</v>
@@ -35754,7 +35754,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="559" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A559" s="2"/>
       <c r="B559" s="2" t="b">
         <v>0</v>
@@ -35800,7 +35800,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="560" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A560" s="2">
         <v>83</v>
       </c>
@@ -35860,7 +35860,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="561" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A561" s="2">
         <v>83</v>
       </c>
@@ -35920,7 +35920,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="562" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A562" s="2">
         <v>83</v>
       </c>
@@ -35980,7 +35980,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="563" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A563" s="2"/>
       <c r="B563" s="2" t="b">
         <v>0</v>
@@ -36038,7 +36038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="564" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A564" s="2"/>
       <c r="B564" s="2" t="b">
         <v>1</v>
@@ -36096,7 +36096,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="565" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A565" s="2"/>
       <c r="B565" s="2" t="b">
         <v>0</v>
@@ -36154,7 +36154,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="566" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A566" s="2">
         <v>85</v>
       </c>
@@ -36214,7 +36214,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="567" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A567" s="2">
         <v>85</v>
       </c>
@@ -36274,7 +36274,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="568" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A568" s="2">
         <v>85</v>
       </c>
@@ -36334,7 +36334,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="569" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A569" s="2">
         <v>86</v>
       </c>
@@ -36394,7 +36394,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="570" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A570" s="2">
         <v>86</v>
       </c>
@@ -36454,7 +36454,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="571" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A571" s="2">
         <v>86</v>
       </c>
@@ -36514,7 +36514,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="572" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A572" s="2">
         <v>84</v>
       </c>
@@ -36574,7 +36574,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="573" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A573" s="2">
         <v>84</v>
       </c>
@@ -36634,7 +36634,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="574" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A574" s="2">
         <v>84</v>
       </c>
@@ -36694,7 +36694,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="575" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A575" s="2"/>
       <c r="B575" s="2" t="b">
         <v>0</v>
@@ -36740,7 +36740,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="576" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A576" s="2">
         <v>80</v>
       </c>
@@ -36796,7 +36796,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="577" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A577" s="2">
         <v>80</v>
       </c>
@@ -36852,7 +36852,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="578" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A578" s="2">
         <v>80</v>
       </c>
@@ -36908,7 +36908,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="579" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A579" s="2">
         <v>80</v>
       </c>
@@ -36964,7 +36964,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="580" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A580" s="2">
         <v>80</v>
       </c>
@@ -37020,7 +37020,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="581" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A581" s="2">
         <v>80</v>
       </c>
@@ -37076,7 +37076,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="582" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A582" s="2">
         <v>80</v>
       </c>
@@ -37132,7 +37132,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="583" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A583" s="2">
         <v>80</v>
       </c>
@@ -37188,7 +37188,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="584" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A584" s="2">
         <v>80</v>
       </c>
@@ -37244,7 +37244,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="585" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A585" s="2"/>
       <c r="B585" s="2" t="b">
         <v>0</v>
@@ -37292,7 +37292,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="586" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A586" s="2">
         <v>91</v>
       </c>
@@ -37348,7 +37348,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="587" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A587" s="2">
         <v>91</v>
       </c>
@@ -37404,7 +37404,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="588" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A588" s="2">
         <v>91</v>
       </c>
@@ -37460,7 +37460,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="589" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A589" s="2">
         <v>91</v>
       </c>
@@ -37516,7 +37516,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="590" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A590" s="2">
         <v>91</v>
       </c>
@@ -37572,7 +37572,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="591" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A591" s="2">
         <v>91</v>
       </c>
@@ -37628,7 +37628,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="592" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A592" s="2">
         <v>91</v>
       </c>
@@ -37684,7 +37684,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="593" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A593" s="2"/>
       <c r="B593" s="2" t="b">
         <v>0</v>
@@ -37738,7 +37738,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="594" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A594" s="2"/>
       <c r="B594" s="2" t="b">
         <v>0</v>
@@ -37792,7 +37792,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="595" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A595" s="2"/>
       <c r="B595" s="2" t="b">
         <v>0</v>
@@ -37846,7 +37846,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="596" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A596" s="2"/>
       <c r="B596" s="2" t="b">
         <v>0</v>
@@ -37900,7 +37900,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="597" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A597" s="2"/>
       <c r="B597" s="2" t="b">
         <v>0</v>
@@ -37954,7 +37954,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="598" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A598" s="2"/>
       <c r="B598" s="2" t="b">
         <v>0</v>
@@ -38008,7 +38008,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="599" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A599" s="2"/>
       <c r="B599" s="2" t="b">
         <v>0</v>
@@ -38062,7 +38062,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="600" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A600" s="2"/>
       <c r="B600" s="2" t="b">
         <v>0</v>
@@ -38116,7 +38116,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="601" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A601" s="2"/>
       <c r="B601" s="2" t="b">
         <v>0</v>
@@ -38170,7 +38170,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="602" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A602" s="2"/>
       <c r="B602" s="2" t="b">
         <v>0</v>
@@ -38222,7 +38222,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="603" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A603" s="2"/>
       <c r="B603" s="2" t="b">
         <v>0</v>
@@ -38274,7 +38274,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="604" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A604" s="2"/>
       <c r="B604" s="2" t="b">
         <v>0</v>
@@ -38326,7 +38326,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="605" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A605" s="2"/>
       <c r="B605" s="2" t="b">
         <v>0</v>
@@ -38378,7 +38378,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="606" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A606" s="2"/>
       <c r="B606" s="2" t="b">
         <v>0</v>
@@ -38430,7 +38430,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="607" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A607" s="2"/>
       <c r="B607" s="2" t="b">
         <v>0</v>
@@ -38482,7 +38482,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="608" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A608" s="2"/>
       <c r="B608" s="2" t="b">
         <v>0</v>
@@ -38534,7 +38534,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="609" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A609" s="2"/>
       <c r="B609" s="2" t="b">
         <v>0</v>
@@ -38586,7 +38586,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="610" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A610" s="2"/>
       <c r="B610" s="2" t="b">
         <v>0</v>
@@ -38638,7 +38638,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="611" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A611" s="2"/>
       <c r="B611" s="2" t="b">
         <v>0</v>
@@ -38690,7 +38690,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="612" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A612" s="2"/>
       <c r="B612" s="2" t="b">
         <v>0</v>
@@ -38740,7 +38740,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="613" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A613" s="2"/>
       <c r="B613" s="2" t="b">
         <v>0</v>
@@ -38790,7 +38790,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="614" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A614" s="2"/>
       <c r="B614" s="2" t="b">
         <v>0</v>
@@ -38838,7 +38838,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="615" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A615" s="2">
         <v>67</v>
       </c>
@@ -38898,7 +38898,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="616" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A616" s="2">
         <v>67</v>
       </c>
@@ -38958,7 +38958,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="617" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A617" s="2">
         <v>67</v>
       </c>
@@ -39018,7 +39018,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="618" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A618" s="2">
         <v>67</v>
       </c>
@@ -39078,7 +39078,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="619" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A619" s="2">
         <v>67</v>
       </c>
@@ -39138,7 +39138,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="620" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A620" s="2"/>
       <c r="B620" s="2" t="b">
         <v>0</v>
@@ -39192,7 +39192,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="621" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A621" s="2"/>
       <c r="B621" s="2" t="b">
         <v>0</v>
@@ -39246,7 +39246,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="622" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A622" s="2"/>
       <c r="B622" s="2" t="b">
         <v>0</v>
@@ -39300,7 +39300,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="623" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A623" s="2"/>
       <c r="B623" s="2" t="b">
         <v>0</v>
@@ -39354,7 +39354,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="624" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A624" s="2"/>
       <c r="B624" s="2" t="b">
         <v>0</v>
@@ -39408,7 +39408,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="625" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A625" s="2"/>
       <c r="B625" s="2" t="b">
         <v>0</v>
@@ -39462,7 +39462,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="626" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A626" s="2"/>
       <c r="B626" s="2" t="b">
         <v>0</v>
@@ -39516,7 +39516,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="627" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A627" s="2"/>
       <c r="B627" s="2" t="b">
         <v>0</v>
@@ -39570,7 +39570,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="628" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A628" s="2"/>
       <c r="B628" s="2" t="b">
         <v>0</v>
@@ -39624,7 +39624,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="629" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A629" s="2"/>
       <c r="B629" s="2" t="b">
         <v>0</v>
@@ -39678,7 +39678,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="630" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A630" s="2"/>
       <c r="B630" s="2" t="b">
         <v>0</v>
@@ -39732,7 +39732,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="631" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A631" s="2"/>
       <c r="B631" s="2" t="b">
         <v>0</v>
@@ -39786,7 +39786,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="632" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A632" s="2"/>
       <c r="B632" s="2" t="b">
         <v>0</v>
@@ -39840,7 +39840,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="633" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A633" s="2"/>
       <c r="B633" s="2" t="b">
         <v>0</v>
@@ -39894,7 +39894,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="634" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A634" s="2">
         <v>77</v>
       </c>
@@ -39950,7 +39950,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="635" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A635" s="2">
         <v>77</v>
       </c>
@@ -40006,7 +40006,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="636" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A636" s="2">
         <v>77</v>
       </c>
@@ -40062,7 +40062,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="637" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A637" s="2">
         <v>77</v>
       </c>
@@ -40118,7 +40118,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="638" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A638" s="2">
         <v>77</v>
       </c>
@@ -40174,7 +40174,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="639" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A639" s="2"/>
       <c r="B639" s="2" t="b">
         <v>0</v>
@@ -40220,7 +40220,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="640" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A640" s="2"/>
       <c r="B640" s="2" t="b">
         <v>0</v>
@@ -40266,7 +40266,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="641" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A641" s="2"/>
       <c r="B641" s="2" t="b">
         <v>0</v>
@@ -40320,7 +40320,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="642" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A642" s="2"/>
       <c r="B642" s="2" t="b">
         <v>0</v>
@@ -40374,7 +40374,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="643" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A643" s="2">
         <v>65</v>
       </c>
@@ -40430,7 +40430,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="644" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A644" s="2">
         <v>65</v>
       </c>
@@ -40486,7 +40486,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="645" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A645" s="2">
         <v>65</v>
       </c>
@@ -40542,7 +40542,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="646" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A646" s="2">
         <v>65</v>
       </c>
@@ -40598,7 +40598,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="647" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A647" s="2">
         <v>65</v>
       </c>
@@ -40654,7 +40654,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="648" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A648" s="2">
         <v>65</v>
       </c>
@@ -40710,7 +40710,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="649" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A649" s="2"/>
       <c r="B649" s="2" t="b">
         <v>0</v>
@@ -40762,7 +40762,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="650" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A650" s="2"/>
       <c r="B650" s="2" t="b">
         <v>0</v>
@@ -40814,7 +40814,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="651" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A651" s="2">
         <v>68</v>
       </c>
@@ -40868,7 +40868,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="652" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A652" s="2">
         <v>68</v>
       </c>
@@ -40922,7 +40922,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="653" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A653" s="2">
         <v>69</v>
       </c>
@@ -40976,7 +40976,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="654" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A654" s="2">
         <v>69</v>
       </c>
@@ -41030,7 +41030,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="655" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A655" s="2">
         <v>69</v>
       </c>
@@ -41084,7 +41084,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="656" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A656" s="2">
         <v>69</v>
       </c>
@@ -41138,7 +41138,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="657" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A657" s="2">
         <v>69</v>
       </c>
@@ -41192,7 +41192,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="658" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A658" s="2">
         <v>69</v>
       </c>
@@ -41246,7 +41246,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="659" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A659" s="2">
         <v>69</v>
       </c>
@@ -41300,7 +41300,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="660" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A660" s="2">
         <v>70</v>
       </c>
@@ -41358,7 +41358,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="661" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A661" s="2">
         <v>70</v>
       </c>
@@ -41416,7 +41416,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="662" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A662" s="2">
         <v>70</v>
       </c>
@@ -41474,7 +41474,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="663" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A663" s="2">
         <v>70</v>
       </c>
@@ -41532,7 +41532,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="664" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A664" s="2">
         <v>70</v>
       </c>
@@ -41590,7 +41590,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="665" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A665" s="2">
         <v>66</v>
       </c>
@@ -41648,7 +41648,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="666" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A666" s="2">
         <v>66</v>
       </c>
@@ -41706,7 +41706,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="667" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A667" s="2">
         <v>66</v>
       </c>
@@ -41764,7 +41764,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="668" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A668" s="2">
         <v>66</v>
       </c>
@@ -41822,7 +41822,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="669" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A669" s="2">
         <v>66</v>
       </c>
@@ -41880,7 +41880,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="670" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A670" s="2">
         <v>71</v>
       </c>
@@ -41938,7 +41938,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="671" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A671" s="2">
         <v>71</v>
       </c>
@@ -41996,7 +41996,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="672" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A672" s="2">
         <v>71</v>
       </c>
@@ -42054,7 +42054,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="673" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A673" s="2">
         <v>71</v>
       </c>
@@ -42112,7 +42112,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="674" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A674" s="2">
         <v>71</v>
       </c>
@@ -42170,7 +42170,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="675" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A675" s="2">
         <v>72</v>
       </c>
@@ -42228,7 +42228,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="676" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A676" s="2">
         <v>72</v>
       </c>
@@ -42286,7 +42286,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="677" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A677" s="2">
         <v>72</v>
       </c>
@@ -42344,7 +42344,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="678" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A678" s="2">
         <v>72</v>
       </c>
@@ -42402,7 +42402,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="679" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A679" s="2">
         <v>72</v>
       </c>
@@ -42460,7 +42460,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="680" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A680" s="2">
         <v>73</v>
       </c>
@@ -42518,7 +42518,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="681" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A681" s="2">
         <v>73</v>
       </c>
@@ -42576,7 +42576,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="682" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A682" s="2">
         <v>73</v>
       </c>
@@ -42634,7 +42634,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="683" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A683" s="2">
         <v>73</v>
       </c>
@@ -42692,7 +42692,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="684" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A684" s="2">
         <v>73</v>
       </c>
@@ -42750,7 +42750,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="685" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A685" s="2"/>
       <c r="B685" s="2" t="b">
         <v>0</v>
@@ -42806,7 +42806,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="686" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A686" s="2"/>
       <c r="B686" s="2" t="b">
         <v>0</v>
@@ -42862,7 +42862,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="687" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A687" s="2"/>
       <c r="B687" s="2" t="b">
         <v>0</v>
@@ -42918,7 +42918,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="688" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A688" s="2"/>
       <c r="B688" s="2" t="b">
         <v>0</v>
@@ -42974,7 +42974,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="689" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A689" s="2"/>
       <c r="B689" s="2" t="b">
         <v>0</v>
@@ -43030,7 +43030,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="690" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A690" s="2"/>
       <c r="B690" s="2" t="b">
         <v>0</v>
@@ -43086,7 +43086,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="691" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A691" s="2"/>
       <c r="B691" s="2" t="b">
         <v>0</v>
@@ -43142,7 +43142,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="692" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A692" s="2"/>
       <c r="B692" s="2" t="b">
         <v>0</v>
@@ -43198,7 +43198,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="693" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A693" s="2"/>
       <c r="B693" s="2" t="b">
         <v>0</v>
@@ -43254,7 +43254,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="694" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A694" s="2"/>
       <c r="B694" s="2" t="b">
         <v>0</v>
@@ -43310,7 +43310,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="695" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A695" s="2"/>
       <c r="B695" s="2" t="b">
         <v>0</v>
@@ -43366,7 +43366,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="696" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A696" s="2"/>
       <c r="B696" s="2" t="b">
         <v>0</v>
@@ -43422,7 +43422,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="697" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A697" s="2"/>
       <c r="B697" s="2" t="b">
         <v>0</v>
@@ -43478,7 +43478,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="698" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A698" s="2"/>
       <c r="B698" s="2" t="b">
         <v>0</v>
@@ -43534,7 +43534,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="699" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A699" s="2"/>
       <c r="B699" s="2" t="b">
         <v>0</v>
@@ -43590,7 +43590,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="700" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A700" s="2"/>
       <c r="B700" s="2" t="b">
         <v>0</v>
@@ -43646,7 +43646,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="701" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A701" s="2"/>
       <c r="B701" s="2" t="b">
         <v>0</v>
@@ -43702,7 +43702,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="702" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A702" s="2"/>
       <c r="B702" s="2" t="b">
         <v>0</v>
@@ -43758,7 +43758,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="703" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A703" s="2"/>
       <c r="B703" s="2" t="b">
         <v>0</v>
@@ -43814,7 +43814,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="704" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A704" s="2"/>
       <c r="B704" s="2" t="b">
         <v>0</v>
@@ -43870,7 +43870,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="705" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A705" s="2"/>
       <c r="B705" s="2" t="b">
         <v>0</v>
@@ -43926,7 +43926,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="706" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A706" s="2"/>
       <c r="B706" s="2" t="b">
         <v>0</v>
@@ -43982,7 +43982,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="707" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A707" s="2"/>
       <c r="B707" s="2" t="b">
         <v>0</v>
@@ -44038,7 +44038,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="708" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A708" s="2"/>
       <c r="B708" s="2" t="b">
         <v>0</v>
@@ -44094,7 +44094,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="709" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A709" s="2"/>
       <c r="B709" s="2" t="b">
         <v>0</v>
@@ -44150,7 +44150,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="710" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A710" s="2"/>
       <c r="B710" s="2" t="b">
         <v>0</v>
@@ -44206,7 +44206,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="711" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A711" s="2"/>
       <c r="B711" s="2" t="b">
         <v>0</v>
@@ -44262,7 +44262,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="712" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A712" s="2"/>
       <c r="B712" s="2" t="b">
         <v>0</v>
@@ -44318,7 +44318,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="713" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A713" s="2"/>
       <c r="B713" s="2" t="b">
         <v>0</v>
@@ -44374,7 +44374,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="714" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A714" s="2"/>
       <c r="B714" s="2" t="b">
         <v>0</v>
@@ -44430,7 +44430,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="715" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A715" s="2"/>
       <c r="B715" s="2" t="b">
         <v>0</v>
@@ -44486,7 +44486,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="716" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A716" s="2"/>
       <c r="B716" s="2" t="b">
         <v>0</v>
@@ -44542,7 +44542,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="717" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A717" s="2"/>
       <c r="B717" s="2" t="b">
         <v>0</v>
@@ -44598,7 +44598,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="718" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A718" s="2"/>
       <c r="B718" s="2" t="b">
         <v>0</v>
@@ -44654,7 +44654,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="719" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A719" s="2"/>
       <c r="B719" s="2" t="b">
         <v>0</v>
@@ -44710,7 +44710,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="720" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A720" s="2"/>
       <c r="B720" s="2" t="b">
         <v>0</v>
@@ -44766,7 +44766,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="721" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A721" s="2"/>
       <c r="B721" s="2" t="b">
         <v>0</v>
@@ -44822,7 +44822,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="722" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A722" s="2"/>
       <c r="B722" s="2" t="b">
         <v>0</v>
@@ -44878,7 +44878,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="723" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A723" s="2"/>
       <c r="B723" s="2" t="b">
         <v>0</v>
@@ -44934,7 +44934,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="724" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A724" s="2"/>
       <c r="B724" s="2" t="b">
         <v>0</v>
@@ -44990,7 +44990,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="725" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A725" s="2"/>
       <c r="B725" s="2" t="b">
         <v>0</v>
@@ -45046,7 +45046,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="726" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A726" s="2"/>
       <c r="B726" s="2" t="b">
         <v>0</v>
@@ -45102,7 +45102,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="727" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A727" s="2"/>
       <c r="B727" s="2" t="b">
         <v>0</v>
@@ -45158,7 +45158,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="728" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A728" s="2"/>
       <c r="B728" s="2" t="b">
         <v>0</v>
@@ -45214,7 +45214,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="729" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A729" s="2"/>
       <c r="B729" s="2" t="b">
         <v>0</v>
@@ -45266,7 +45266,7 @@
         <v>72686</v>
       </c>
     </row>
-    <row r="730" spans="1:20" ht="18" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A730" s="2"/>
       <c r="B730" s="2" t="b">
         <v>0</v>

--- a/primary_survey/v2025/conf/nvi_answer_key_20260316.xlsx
+++ b/primary_survey/v2025/conf/nvi_answer_key_20260316.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mike\Desktop\2_responsibilities\nvi_etl\primary_survey\v2025\conf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE27324-B19E-4A8E-9EE9-37129785C0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A05F04B1-1599-4FFA-91C9-5F01F740BF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2590" yWindow="2180" windowWidth="21600" windowHeight="13070" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E6AADBC4-36D9-4E0B-9CAE-3CD032CDA67A}"/>
   </bookViews>
   <sheets>
     <sheet name="indicator_main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6221" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6221" uniqueCount="744">
   <si>
     <t>indicator_include</t>
   </si>
@@ -2275,6 +2275,9 @@
   </si>
   <si>
     <t>survey_question_type</t>
+  </si>
+  <si>
+    <t>Youth_in_Household_Under5 == 1</t>
   </si>
 </sst>
 </file>
@@ -3325,29 +3328,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEFEB3D-797E-4D61-9833-8A6B2512670D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:U730"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="25.453125" style="3" customWidth="1"/>
+    <col min="1" max="2" width="25.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="29" style="3" customWidth="1"/>
-    <col min="4" max="5" width="34.1796875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="53.54296875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="52.1796875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="51.26953125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="22.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="25.453125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.453125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="25.453125" style="3" customWidth="1"/>
+    <col min="4" max="5" width="34.140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="53.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="52.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="51.28515625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="25.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" style="1" customWidth="1"/>
+    <col min="12" max="13" width="25.42578125" style="3" customWidth="1"/>
     <col min="14" max="14" width="118" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.453125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="43.81640625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="35.81640625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="25.453125" style="3" customWidth="1"/>
-    <col min="19" max="20" width="25.453125" style="11" customWidth="1"/>
-    <col min="21" max="21" width="36.36328125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="8.7265625" style="1"/>
+    <col min="15" max="15" width="25.42578125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="43.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="35.85546875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="25.42578125" style="3" customWidth="1"/>
+    <col min="19" max="20" width="25.42578125" style="11" customWidth="1"/>
+    <col min="21" max="21" width="36.42578125" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="18" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>512</v>
       </c>
@@ -3412,7 +3415,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3475,7 +3478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3538,7 +3541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3601,7 +3604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -3664,7 +3667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -3727,7 +3730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -3790,7 +3793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2</v>
       </c>
@@ -3853,7 +3856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2</v>
       </c>
@@ -3916,7 +3919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2</v>
       </c>
@@ -3979,7 +3982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2</v>
       </c>
@@ -4042,7 +4045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>2</v>
       </c>
@@ -4105,7 +4108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>2</v>
       </c>
@@ -4168,7 +4171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -4231,7 +4234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -4294,7 +4297,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>3</v>
       </c>
@@ -4357,7 +4360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>3</v>
       </c>
@@ -4420,7 +4423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>3</v>
       </c>
@@ -4483,7 +4486,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>3</v>
       </c>
@@ -4546,7 +4549,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>3</v>
       </c>
@@ -4609,7 +4612,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>3</v>
       </c>
@@ -4672,7 +4675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -4735,7 +4738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>3</v>
       </c>
@@ -4798,7 +4801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>3</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>3</v>
       </c>
@@ -4924,7 +4927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>3</v>
       </c>
@@ -4987,7 +4990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>3</v>
       </c>
@@ -5050,7 +5053,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>3</v>
       </c>
@@ -5113,7 +5116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>3</v>
       </c>
@@ -5176,7 +5179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>3</v>
       </c>
@@ -5239,7 +5242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>3</v>
       </c>
@@ -5302,7 +5305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>3</v>
       </c>
@@ -5365,7 +5368,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>3</v>
       </c>
@@ -5428,7 +5431,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>3</v>
       </c>
@@ -5491,7 +5494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>3</v>
       </c>
@@ -5554,7 +5557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>3</v>
       </c>
@@ -5617,7 +5620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>3</v>
       </c>
@@ -5680,7 +5683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>3</v>
       </c>
@@ -5743,7 +5746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>3</v>
       </c>
@@ -5806,7 +5809,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>3</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>3</v>
       </c>
@@ -5932,7 +5935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>3</v>
       </c>
@@ -5995,7 +5998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>3</v>
       </c>
@@ -6058,7 +6061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>3</v>
       </c>
@@ -6121,7 +6124,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>3</v>
       </c>
@@ -6184,7 +6187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>5</v>
       </c>
@@ -6247,7 +6250,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>5</v>
       </c>
@@ -6310,7 +6313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>5</v>
       </c>
@@ -6373,7 +6376,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>5</v>
       </c>
@@ -6436,7 +6439,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>6</v>
       </c>
@@ -6495,7 +6498,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>6</v>
       </c>
@@ -6554,7 +6557,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>6</v>
       </c>
@@ -6613,7 +6616,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>6</v>
       </c>
@@ -6672,7 +6675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>6</v>
       </c>
@@ -6731,7 +6734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>6</v>
       </c>
@@ -6790,7 +6793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>6</v>
       </c>
@@ -6849,7 +6852,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>9</v>
       </c>
@@ -6908,7 +6911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>9</v>
       </c>
@@ -6967,7 +6970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>9</v>
       </c>
@@ -7026,7 +7029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>9</v>
       </c>
@@ -7085,7 +7088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>9</v>
       </c>
@@ -7144,7 +7147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>16</v>
       </c>
@@ -7203,7 +7206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>16</v>
       </c>
@@ -7262,7 +7265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>18</v>
       </c>
@@ -7325,7 +7328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>18</v>
       </c>
@@ -7388,7 +7391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>18</v>
       </c>
@@ -7451,7 +7454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>18</v>
       </c>
@@ -7514,7 +7517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>19</v>
       </c>
@@ -7577,7 +7580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>19</v>
       </c>
@@ -7640,7 +7643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>19</v>
       </c>
@@ -7703,7 +7706,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>20</v>
       </c>
@@ -7762,7 +7765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>20</v>
       </c>
@@ -7821,7 +7824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>20</v>
       </c>
@@ -7880,7 +7883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>20</v>
       </c>
@@ -7939,7 +7942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>20</v>
       </c>
@@ -7998,7 +8001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>22</v>
       </c>
@@ -8061,7 +8064,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>22</v>
       </c>
@@ -8124,7 +8127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>22</v>
       </c>
@@ -8187,7 +8190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>22</v>
       </c>
@@ -8250,7 +8253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>22</v>
       </c>
@@ -8313,7 +8316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>23</v>
       </c>
@@ -8376,7 +8379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>23</v>
       </c>
@@ -8439,7 +8442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>23</v>
       </c>
@@ -8502,7 +8505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>23</v>
       </c>
@@ -8565,7 +8568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>23</v>
       </c>
@@ -8628,7 +8631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>23</v>
       </c>
@@ -8691,7 +8694,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>25</v>
       </c>
@@ -8754,7 +8757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>25</v>
       </c>
@@ -8817,7 +8820,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>25</v>
       </c>
@@ -8880,7 +8883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>25</v>
       </c>
@@ -8943,7 +8946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>25</v>
       </c>
@@ -9006,7 +9009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>25</v>
       </c>
@@ -9069,7 +9072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>26</v>
       </c>
@@ -9132,7 +9135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>26</v>
       </c>
@@ -9195,7 +9198,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>26</v>
       </c>
@@ -9258,7 +9261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>26</v>
       </c>
@@ -9321,7 +9324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>26</v>
       </c>
@@ -9384,7 +9387,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>26</v>
       </c>
@@ -9447,7 +9450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>27</v>
       </c>
@@ -9510,7 +9513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>27</v>
       </c>
@@ -9573,7 +9576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>27</v>
       </c>
@@ -9636,7 +9639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>27</v>
       </c>
@@ -9699,7 +9702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>27</v>
       </c>
@@ -9762,7 +9765,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>27</v>
       </c>
@@ -9825,7 +9828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>29</v>
       </c>
@@ -9888,7 +9891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>29</v>
       </c>
@@ -9951,7 +9954,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>29</v>
       </c>
@@ -10014,7 +10017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>29</v>
       </c>
@@ -10077,7 +10080,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>29</v>
       </c>
@@ -10140,7 +10143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>33</v>
       </c>
@@ -10203,7 +10206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>33</v>
       </c>
@@ -10266,7 +10269,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>33</v>
       </c>
@@ -10329,7 +10332,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>33</v>
       </c>
@@ -10392,7 +10395,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>33</v>
       </c>
@@ -10455,7 +10458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>33</v>
       </c>
@@ -10518,7 +10521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>33</v>
       </c>
@@ -10581,7 +10584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>33</v>
       </c>
@@ -10644,7 +10647,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>33</v>
       </c>
@@ -10707,7 +10710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>33</v>
       </c>
@@ -10770,7 +10773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>33</v>
       </c>
@@ -10833,7 +10836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>33</v>
       </c>
@@ -10896,7 +10899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>33</v>
       </c>
@@ -10959,7 +10962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>33</v>
       </c>
@@ -11022,7 +11025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>33</v>
       </c>
@@ -11085,7 +11088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>33</v>
       </c>
@@ -11148,7 +11151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>33</v>
       </c>
@@ -11211,7 +11214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>33</v>
       </c>
@@ -11274,7 +11277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>33</v>
       </c>
@@ -11337,7 +11340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>33</v>
       </c>
@@ -11400,7 +11403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>33</v>
       </c>
@@ -11463,7 +11466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>33</v>
       </c>
@@ -11526,7 +11529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>33</v>
       </c>
@@ -11589,7 +11592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>33</v>
       </c>
@@ -11652,7 +11655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>34</v>
       </c>
@@ -11715,7 +11718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>34</v>
       </c>
@@ -11778,7 +11781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>34</v>
       </c>
@@ -11841,7 +11844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>34</v>
       </c>
@@ -11904,7 +11907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>34</v>
       </c>
@@ -11967,7 +11970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>34</v>
       </c>
@@ -12030,7 +12033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>35</v>
       </c>
@@ -12093,7 +12096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>35</v>
       </c>
@@ -12156,7 +12159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>35</v>
       </c>
@@ -12219,7 +12222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>35</v>
       </c>
@@ -12282,7 +12285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>35</v>
       </c>
@@ -12345,7 +12348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>35</v>
       </c>
@@ -12408,7 +12411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>36</v>
       </c>
@@ -12471,7 +12474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>36</v>
       </c>
@@ -12534,7 +12537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>36</v>
       </c>
@@ -12597,7 +12600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>36</v>
       </c>
@@ -12660,7 +12663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>36</v>
       </c>
@@ -12723,7 +12726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>36</v>
       </c>
@@ -12786,7 +12789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>37</v>
       </c>
@@ -12849,7 +12852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>37</v>
       </c>
@@ -12912,7 +12915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>37</v>
       </c>
@@ -12975,7 +12978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>37</v>
       </c>
@@ -13038,7 +13041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>37</v>
       </c>
@@ -13101,7 +13104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>37</v>
       </c>
@@ -13164,7 +13167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>37</v>
       </c>
@@ -13227,7 +13230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>37</v>
       </c>
@@ -13290,7 +13293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>37</v>
       </c>
@@ -13353,7 +13356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>37</v>
       </c>
@@ -13416,7 +13419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>38</v>
       </c>
@@ -13479,7 +13482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>38</v>
       </c>
@@ -13542,7 +13545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>38</v>
       </c>
@@ -13605,7 +13608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>38</v>
       </c>
@@ -13668,7 +13671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>38</v>
       </c>
@@ -13731,7 +13734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>39</v>
       </c>
@@ -13790,7 +13793,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>39</v>
       </c>
@@ -13849,7 +13852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>39</v>
       </c>
@@ -13908,7 +13911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>39</v>
       </c>
@@ -13967,7 +13970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>39</v>
       </c>
@@ -14026,7 +14029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>40</v>
       </c>
@@ -14089,7 +14092,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>40</v>
       </c>
@@ -14152,7 +14155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>40</v>
       </c>
@@ -14215,7 +14218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>40</v>
       </c>
@@ -14278,7 +14281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>40</v>
       </c>
@@ -14341,7 +14344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>41</v>
       </c>
@@ -14404,7 +14407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>41</v>
       </c>
@@ -14467,7 +14470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>41</v>
       </c>
@@ -14530,7 +14533,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>41</v>
       </c>
@@ -14593,7 +14596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>41</v>
       </c>
@@ -14656,7 +14659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>42</v>
       </c>
@@ -14719,7 +14722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>42</v>
       </c>
@@ -14782,7 +14785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>42</v>
       </c>
@@ -14845,7 +14848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>42</v>
       </c>
@@ -14908,7 +14911,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
         <v>42</v>
       </c>
@@ -14971,7 +14974,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
         <v>43</v>
       </c>
@@ -15034,7 +15037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
         <v>43</v>
       </c>
@@ -15097,7 +15100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
         <v>43</v>
       </c>
@@ -15160,7 +15163,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
         <v>43</v>
       </c>
@@ -15223,7 +15226,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>44</v>
       </c>
@@ -15282,7 +15285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>44</v>
       </c>
@@ -15341,7 +15344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>44</v>
       </c>
@@ -15400,7 +15403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>44</v>
       </c>
@@ -15459,7 +15462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>44</v>
       </c>
@@ -15518,7 +15521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>45</v>
       </c>
@@ -15581,7 +15584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>45</v>
       </c>
@@ -15644,7 +15647,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>45</v>
       </c>
@@ -15707,7 +15710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>45</v>
       </c>
@@ -15770,7 +15773,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>45</v>
       </c>
@@ -15833,7 +15836,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>45</v>
       </c>
@@ -15896,7 +15899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>46</v>
       </c>
@@ -15959,7 +15962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>46</v>
       </c>
@@ -16022,7 +16025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>46</v>
       </c>
@@ -16085,7 +16088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>47</v>
       </c>
@@ -16148,7 +16151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
         <v>47</v>
       </c>
@@ -16211,7 +16214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>47</v>
       </c>
@@ -16274,7 +16277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>47</v>
       </c>
@@ -16337,7 +16340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>47</v>
       </c>
@@ -16400,7 +16403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>47</v>
       </c>
@@ -16463,7 +16466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>47</v>
       </c>
@@ -16526,7 +16529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>47</v>
       </c>
@@ -16589,7 +16592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>47</v>
       </c>
@@ -16652,7 +16655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>47</v>
       </c>
@@ -16715,7 +16718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>47</v>
       </c>
@@ -16778,7 +16781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>47</v>
       </c>
@@ -16841,7 +16844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>47</v>
       </c>
@@ -16904,7 +16907,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>47</v>
       </c>
@@ -16967,7 +16970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>47</v>
       </c>
@@ -17030,7 +17033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>47</v>
       </c>
@@ -17093,7 +17096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>47</v>
       </c>
@@ -17156,7 +17159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>47</v>
       </c>
@@ -17219,7 +17222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
         <v>47</v>
       </c>
@@ -17282,7 +17285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>47</v>
       </c>
@@ -17345,7 +17348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>47</v>
       </c>
@@ -17408,7 +17411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
         <v>47</v>
       </c>
@@ -17471,7 +17474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>47</v>
       </c>
@@ -17534,7 +17537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>47</v>
       </c>
@@ -17597,7 +17600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>47</v>
       </c>
@@ -17660,7 +17663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>47</v>
       </c>
@@ -17723,7 +17726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>47</v>
       </c>
@@ -17786,7 +17789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
         <v>47</v>
       </c>
@@ -17849,7 +17852,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>47</v>
       </c>
@@ -17912,7 +17915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>47</v>
       </c>
@@ -17975,7 +17978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>47</v>
       </c>
@@ -18038,7 +18041,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>47</v>
       </c>
@@ -18101,7 +18104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
         <v>47</v>
       </c>
@@ -18164,7 +18167,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>47</v>
       </c>
@@ -18227,7 +18230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>47</v>
       </c>
@@ -18290,7 +18293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
         <v>47</v>
       </c>
@@ -18353,7 +18356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
         <v>47</v>
       </c>
@@ -18416,7 +18419,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
         <v>47</v>
       </c>
@@ -18479,7 +18482,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
         <v>47</v>
       </c>
@@ -18542,7 +18545,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>47</v>
       </c>
@@ -18605,7 +18608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>47</v>
       </c>
@@ -18668,7 +18671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>47</v>
       </c>
@@ -18731,7 +18734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>47</v>
       </c>
@@ -18794,7 +18797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
         <v>47</v>
       </c>
@@ -18857,7 +18860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>47</v>
       </c>
@@ -18920,7 +18923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
         <v>48</v>
       </c>
@@ -18977,7 +18980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
         <v>48</v>
       </c>
@@ -19034,7 +19037,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
         <v>48</v>
       </c>
@@ -19091,7 +19094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
         <v>48</v>
       </c>
@@ -19148,7 +19151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>48</v>
       </c>
@@ -19205,7 +19208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
         <v>48</v>
       </c>
@@ -19262,7 +19265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
         <v>49</v>
       </c>
@@ -19321,7 +19324,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>49</v>
       </c>
@@ -19380,7 +19383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
         <v>49</v>
       </c>
@@ -19439,7 +19442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>49</v>
       </c>
@@ -19498,7 +19501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
         <v>49</v>
       </c>
@@ -19557,7 +19560,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
         <v>50</v>
       </c>
@@ -19616,7 +19619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
         <v>50</v>
       </c>
@@ -19675,7 +19678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
         <v>50</v>
       </c>
@@ -19734,7 +19737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>50</v>
       </c>
@@ -19793,7 +19796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
         <v>51</v>
       </c>
@@ -19852,7 +19855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
         <v>51</v>
       </c>
@@ -19911,7 +19914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A267" s="2">
         <v>51</v>
       </c>
@@ -19970,7 +19973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A268" s="2">
         <v>51</v>
       </c>
@@ -20029,7 +20032,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A269" s="2">
         <v>52</v>
       </c>
@@ -20088,7 +20091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="270" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A270" s="2">
         <v>52</v>
       </c>
@@ -20147,7 +20150,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A271" s="2">
         <v>52</v>
       </c>
@@ -20206,7 +20209,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>52</v>
       </c>
@@ -20265,7 +20268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>52</v>
       </c>
@@ -20324,7 +20327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="274" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>53</v>
       </c>
@@ -20387,7 +20390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>53</v>
       </c>
@@ -20450,7 +20453,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>53</v>
       </c>
@@ -20513,7 +20516,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>54</v>
       </c>
@@ -20572,7 +20575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="278" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>54</v>
       </c>
@@ -20631,7 +20634,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>54</v>
       </c>
@@ -20690,7 +20693,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="280" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>54</v>
       </c>
@@ -20749,7 +20752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="281" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A281" s="2">
         <v>54</v>
       </c>
@@ -20808,7 +20811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A282" s="2">
         <v>54</v>
       </c>
@@ -20867,7 +20870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="283" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A283" s="2">
         <v>55</v>
       </c>
@@ -20930,7 +20933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A284" s="2">
         <v>55</v>
       </c>
@@ -20993,7 +20996,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A285" s="2">
         <v>55</v>
       </c>
@@ -21056,7 +21059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A286" s="2">
         <v>56</v>
       </c>
@@ -21115,7 +21118,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A287" s="2">
         <v>56</v>
       </c>
@@ -21174,7 +21177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A288" s="2">
         <v>56</v>
       </c>
@@ -21233,7 +21236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A289" s="2">
         <v>56</v>
       </c>
@@ -21292,7 +21295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A290" s="2">
         <v>56</v>
       </c>
@@ -21351,7 +21354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A291" s="2">
         <v>56</v>
       </c>
@@ -21410,7 +21413,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="292" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A292" s="2">
         <v>56</v>
       </c>
@@ -21469,7 +21472,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A293" s="2">
         <v>56</v>
       </c>
@@ -21528,7 +21531,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="294" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A294" s="2">
         <v>57</v>
       </c>
@@ -21587,7 +21590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>57</v>
       </c>
@@ -21646,7 +21649,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>57</v>
       </c>
@@ -21705,7 +21708,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>57</v>
       </c>
@@ -21764,7 +21767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>57</v>
       </c>
@@ -21823,7 +21826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>57</v>
       </c>
@@ -21882,7 +21885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>57</v>
       </c>
@@ -21941,7 +21944,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>57</v>
       </c>
@@ -22000,7 +22003,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="302" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>58</v>
       </c>
@@ -22059,7 +22062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>58</v>
       </c>
@@ -22118,7 +22121,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>62</v>
       </c>
@@ -22177,7 +22180,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>62</v>
       </c>
@@ -22236,7 +22239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>59</v>
       </c>
@@ -22299,7 +22302,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>59</v>
       </c>
@@ -22362,7 +22365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>59</v>
       </c>
@@ -22425,7 +22428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>59</v>
       </c>
@@ -22488,7 +22491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>59</v>
       </c>
@@ -22551,7 +22554,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>60</v>
       </c>
@@ -22614,7 +22617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>60</v>
       </c>
@@ -22677,7 +22680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>60</v>
       </c>
@@ -22740,7 +22743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>60</v>
       </c>
@@ -22803,7 +22806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>60</v>
       </c>
@@ -22866,7 +22869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>61</v>
       </c>
@@ -22925,7 +22928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>61</v>
       </c>
@@ -22984,7 +22987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>61</v>
       </c>
@@ -23043,7 +23046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>61</v>
       </c>
@@ -23102,7 +23105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>61</v>
       </c>
@@ -23161,7 +23164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>61</v>
       </c>
@@ -23220,7 +23223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>62</v>
       </c>
@@ -23283,7 +23286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>62</v>
       </c>
@@ -23346,7 +23349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>64</v>
       </c>
@@ -23403,7 +23406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>64</v>
       </c>
@@ -23460,7 +23463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>64</v>
       </c>
@@ -23517,7 +23520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>64</v>
       </c>
@@ -23574,7 +23577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>64</v>
       </c>
@@ -23631,7 +23634,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>89</v>
       </c>
@@ -23694,7 +23697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>89</v>
       </c>
@@ -23757,7 +23760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>89</v>
       </c>
@@ -23820,7 +23823,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>90</v>
       </c>
@@ -23883,7 +23886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>90</v>
       </c>
@@ -23946,7 +23949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>90</v>
       </c>
@@ -24009,7 +24012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>88</v>
       </c>
@@ -24072,7 +24075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>88</v>
       </c>
@@ -24135,7 +24138,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>88</v>
       </c>
@@ -24196,7 +24199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A338" s="2"/>
       <c r="B338" s="2" t="b">
         <v>0</v>
@@ -24253,7 +24256,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A339" s="2"/>
       <c r="B339" s="2" t="b">
         <v>0</v>
@@ -24310,7 +24313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A340" s="2"/>
       <c r="B340" s="2" t="b">
         <v>0</v>
@@ -24367,7 +24370,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A341" s="2"/>
       <c r="B341" s="2" t="b">
         <v>0</v>
@@ -24424,7 +24427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A342" s="2"/>
       <c r="B342" s="2" t="b">
         <v>0</v>
@@ -24481,7 +24484,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A343" s="2"/>
       <c r="B343" s="2" t="b">
         <v>0</v>
@@ -24538,7 +24541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A344" s="2"/>
       <c r="B344" s="2" t="b">
         <v>0</v>
@@ -24595,7 +24598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>82</v>
       </c>
@@ -24658,7 +24661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>82</v>
       </c>
@@ -24721,7 +24724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>82</v>
       </c>
@@ -24784,7 +24787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>82</v>
       </c>
@@ -24847,7 +24850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A349" s="2">
         <v>82</v>
       </c>
@@ -24910,7 +24913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A350" s="2">
         <v>82</v>
       </c>
@@ -24973,7 +24976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A351" s="2">
         <v>81</v>
       </c>
@@ -25036,7 +25039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A352" s="2">
         <v>81</v>
       </c>
@@ -25099,7 +25102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A353" s="2">
         <v>81</v>
       </c>
@@ -25162,7 +25165,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A354" s="2">
         <v>81</v>
       </c>
@@ -25225,7 +25228,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A355" s="2">
         <v>81</v>
       </c>
@@ -25288,7 +25291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A356" s="2">
         <v>81</v>
       </c>
@@ -25351,7 +25354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A357" s="2">
         <v>76</v>
       </c>
@@ -25414,7 +25417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A358" s="2">
         <v>76</v>
       </c>
@@ -25477,7 +25480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A359" s="2">
         <v>76</v>
       </c>
@@ -25540,7 +25543,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A360" s="2">
         <v>76</v>
       </c>
@@ -25603,7 +25606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A361" s="2">
         <v>75</v>
       </c>
@@ -25666,7 +25669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A362" s="2">
         <v>75</v>
       </c>
@@ -25729,7 +25732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A363" s="2">
         <v>75</v>
       </c>
@@ -25792,7 +25795,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A364" s="2">
         <v>75</v>
       </c>
@@ -25855,7 +25858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A365" s="2">
         <v>74</v>
       </c>
@@ -25914,7 +25917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A366" s="2">
         <v>74</v>
       </c>
@@ -25973,7 +25976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A367" s="2">
         <v>74</v>
       </c>
@@ -26032,7 +26035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A368" s="2">
         <v>74</v>
       </c>
@@ -26091,7 +26094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A369" s="2">
         <v>74</v>
       </c>
@@ -26150,7 +26153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A370" s="2">
         <v>87</v>
       </c>
@@ -26213,7 +26216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A371" s="2">
         <v>87</v>
       </c>
@@ -26276,7 +26279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A372" s="2">
         <v>94</v>
       </c>
@@ -26335,7 +26338,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="373" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A373" s="2">
         <v>94</v>
       </c>
@@ -26394,7 +26397,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A374" s="2">
         <v>94</v>
       </c>
@@ -26453,7 +26456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A375" s="2">
         <v>94</v>
       </c>
@@ -26512,7 +26515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A376" s="2">
         <v>94</v>
       </c>
@@ -26571,7 +26574,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A377" s="2">
         <v>94</v>
       </c>
@@ -26630,7 +26633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A378" s="2">
         <v>94</v>
       </c>
@@ -26689,7 +26692,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A379" s="2">
         <v>94</v>
       </c>
@@ -26748,7 +26751,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A380" s="2">
         <v>94</v>
       </c>
@@ -26807,7 +26810,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A381" s="2">
         <v>94</v>
       </c>
@@ -26866,7 +26869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="382" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A382" s="2">
         <v>94</v>
       </c>
@@ -26925,7 +26928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="383" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A383" s="2">
         <v>94</v>
       </c>
@@ -26984,7 +26987,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A384" s="2">
         <v>94</v>
       </c>
@@ -27043,7 +27046,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="385" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A385" s="2"/>
       <c r="B385" s="2" t="b">
         <v>0</v>
@@ -27104,7 +27107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A386" s="2"/>
       <c r="B386" s="2" t="b">
         <v>0</v>
@@ -27165,7 +27168,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A387" s="2"/>
       <c r="B387" s="2" t="b">
         <v>0</v>
@@ -27226,7 +27229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A388" s="2"/>
       <c r="B388" s="2" t="b">
         <v>0</v>
@@ -27287,7 +27290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A389" s="2"/>
       <c r="B389" s="2" t="b">
         <v>0</v>
@@ -27348,7 +27351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A390" s="2">
         <v>79</v>
       </c>
@@ -27411,7 +27414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A391" s="2">
         <v>79</v>
       </c>
@@ -27474,7 +27477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A392" s="2">
         <v>79</v>
       </c>
@@ -27537,7 +27540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A393" s="2">
         <v>79</v>
       </c>
@@ -27600,7 +27603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A394" s="2">
         <v>79</v>
       </c>
@@ -27663,7 +27666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A395" s="2">
         <v>78</v>
       </c>
@@ -27726,7 +27729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A396" s="2">
         <v>78</v>
       </c>
@@ -27789,7 +27792,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A397" s="2">
         <v>78</v>
       </c>
@@ -27852,7 +27855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A398" s="2">
         <v>78</v>
       </c>
@@ -27915,7 +27918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A399" s="2">
         <v>78</v>
       </c>
@@ -27978,7 +27981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A400" s="2"/>
       <c r="B400" s="2" t="b">
         <v>0</v>
@@ -28039,7 +28042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A401" s="2"/>
       <c r="B401" s="2" t="b">
         <v>0</v>
@@ -28100,7 +28103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A402" s="2"/>
       <c r="B402" s="2" t="b">
         <v>0</v>
@@ -28161,7 +28164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A403" s="2"/>
       <c r="B403" s="2" t="b">
         <v>0</v>
@@ -28222,7 +28225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A404" s="2"/>
       <c r="B404" s="2" t="b">
         <v>0</v>
@@ -28283,7 +28286,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A405" s="2"/>
       <c r="B405" s="2" t="b">
         <v>0</v>
@@ -28344,7 +28347,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A406" s="2"/>
       <c r="B406" s="2" t="b">
         <v>0</v>
@@ -28405,7 +28408,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A407" s="2"/>
       <c r="B407" s="2" t="b">
         <v>0</v>
@@ -28466,7 +28469,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A408" s="2"/>
       <c r="B408" s="2" t="b">
         <v>0</v>
@@ -28527,7 +28530,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A409" s="2"/>
       <c r="B409" s="2" t="b">
         <v>0</v>
@@ -28588,7 +28591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A410" s="2"/>
       <c r="B410" s="2" t="b">
         <v>0</v>
@@ -28649,7 +28652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A411" s="2"/>
       <c r="B411" s="2" t="b">
         <v>0</v>
@@ -28710,7 +28713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A412" s="2"/>
       <c r="B412" s="2" t="b">
         <v>0</v>
@@ -28771,7 +28774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="413" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A413" s="2"/>
       <c r="B413" s="2" t="b">
         <v>0</v>
@@ -28832,7 +28835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="414" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A414" s="2"/>
       <c r="B414" s="2" t="b">
         <v>0</v>
@@ -28893,7 +28896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="415" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A415" s="2"/>
       <c r="B415" s="2" t="b">
         <v>0</v>
@@ -28954,7 +28957,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A416" s="2"/>
       <c r="B416" s="2" t="b">
         <v>0</v>
@@ -29015,7 +29018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="417" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A417" s="2"/>
       <c r="B417" s="2" t="b">
         <v>0</v>
@@ -29076,7 +29079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A418" s="2"/>
       <c r="B418" s="2" t="b">
         <v>0</v>
@@ -29137,7 +29140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A419" s="2"/>
       <c r="B419" s="2" t="b">
         <v>0</v>
@@ -29198,7 +29201,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A420" s="2"/>
       <c r="B420" s="2" t="b">
         <v>0</v>
@@ -29259,7 +29262,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A421" s="2"/>
       <c r="B421" s="2" t="b">
         <v>0</v>
@@ -29320,7 +29323,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A422" s="2"/>
       <c r="B422" s="2" t="b">
         <v>0</v>
@@ -29381,7 +29384,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="423" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A423" s="2"/>
       <c r="B423" s="2" t="b">
         <v>0</v>
@@ -29442,7 +29445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A424" s="2"/>
       <c r="B424" s="2" t="b">
         <v>0</v>
@@ -29503,7 +29506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A425" s="2"/>
       <c r="B425" s="2" t="b">
         <v>0</v>
@@ -29564,7 +29567,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="426" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A426" s="2"/>
       <c r="B426" s="2" t="b">
         <v>0</v>
@@ -29625,7 +29628,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="427" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A427" s="2"/>
       <c r="B427" s="2" t="b">
         <v>0</v>
@@ -29686,7 +29689,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A428" s="2"/>
       <c r="B428" s="2" t="b">
         <v>0</v>
@@ -29747,7 +29750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="429" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A429" s="2"/>
       <c r="B429" s="2" t="b">
         <v>0</v>
@@ -29808,7 +29811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="430" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A430" s="2"/>
       <c r="B430" s="2" t="b">
         <v>0</v>
@@ -29869,7 +29872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A431" s="2"/>
       <c r="B431" s="2" t="b">
         <v>0</v>
@@ -29930,7 +29933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A432" s="2"/>
       <c r="B432" s="2" t="b">
         <v>0</v>
@@ -29991,7 +29994,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="433" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A433" s="2"/>
       <c r="B433" s="2" t="b">
         <v>0</v>
@@ -30052,7 +30055,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="434" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A434" s="2"/>
       <c r="B434" s="2" t="b">
         <v>0</v>
@@ -30113,7 +30116,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A435" s="2"/>
       <c r="B435" s="2" t="b">
         <v>0</v>
@@ -30174,7 +30177,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="436" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A436" s="2"/>
       <c r="B436" s="2" t="b">
         <v>0</v>
@@ -30235,7 +30238,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A437" s="2"/>
       <c r="B437" s="2" t="b">
         <v>0</v>
@@ -30296,7 +30299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="438" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A438" s="2"/>
       <c r="B438" s="2" t="b">
         <v>0</v>
@@ -30357,7 +30360,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A439" s="2"/>
       <c r="B439" s="2" t="b">
         <v>0</v>
@@ -30418,7 +30421,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A440" s="2"/>
       <c r="B440" s="2" t="b">
         <v>0</v>
@@ -30479,7 +30482,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A441" s="2"/>
       <c r="B441" s="2" t="b">
         <v>0</v>
@@ -30540,7 +30543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A442" s="2"/>
       <c r="B442" s="2" t="b">
         <v>0</v>
@@ -30601,7 +30604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A443" s="2"/>
       <c r="B443" s="2" t="b">
         <v>0</v>
@@ -30662,7 +30665,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A444" s="2"/>
       <c r="B444" s="2" t="b">
         <v>0</v>
@@ -30723,7 +30726,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A445" s="2"/>
       <c r="B445" s="2" t="b">
         <v>0</v>
@@ -30784,7 +30787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A446" s="2"/>
       <c r="B446" s="2" t="b">
         <v>0</v>
@@ -30845,7 +30848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="447" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A447" s="2"/>
       <c r="B447" s="2" t="b">
         <v>0</v>
@@ -30906,7 +30909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="448" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A448" s="2"/>
       <c r="B448" s="2" t="b">
         <v>0</v>
@@ -30967,7 +30970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A449" s="2"/>
       <c r="B449" s="2" t="b">
         <v>0</v>
@@ -31028,7 +31031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A450" s="2"/>
       <c r="B450" s="2" t="b">
         <v>0</v>
@@ -31089,7 +31092,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="451" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A451" s="2"/>
       <c r="B451" s="2" t="b">
         <v>0</v>
@@ -31150,7 +31153,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A452" s="2"/>
       <c r="B452" s="2" t="b">
         <v>0</v>
@@ -31211,7 +31214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A453" s="2"/>
       <c r="B453" s="2" t="b">
         <v>0</v>
@@ -31268,7 +31271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="454" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A454" s="2"/>
       <c r="B454" s="2" t="b">
         <v>0</v>
@@ -31325,7 +31328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A455" s="2"/>
       <c r="B455" s="2" t="b">
         <v>0</v>
@@ -31382,7 +31385,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="456" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A456" s="2"/>
       <c r="B456" s="2" t="b">
         <v>0</v>
@@ -31439,7 +31442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="457" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A457" s="2"/>
       <c r="B457" s="2" t="b">
         <v>0</v>
@@ -31496,7 +31499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A458" s="2"/>
       <c r="B458" s="2" t="b">
         <v>0</v>
@@ -31553,7 +31556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="459" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A459" s="2"/>
       <c r="B459" s="2" t="b">
         <v>0</v>
@@ -31610,7 +31613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A460" s="2"/>
       <c r="B460" s="2" t="b">
         <v>0</v>
@@ -31667,7 +31670,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="461" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A461" s="2"/>
       <c r="B461" s="2" t="b">
         <v>0</v>
@@ -31724,7 +31727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="462" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A462" s="2"/>
       <c r="B462" s="2" t="b">
         <v>0</v>
@@ -31781,7 +31784,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A463" s="2"/>
       <c r="B463" s="2" t="b">
         <v>0</v>
@@ -31838,7 +31841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="464" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A464" s="2"/>
       <c r="B464" s="2" t="b">
         <v>0</v>
@@ -31895,7 +31898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="465" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A465" s="2"/>
       <c r="B465" s="2" t="b">
         <v>0</v>
@@ -31952,7 +31955,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="466" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A466" s="2"/>
       <c r="B466" s="2" t="b">
         <v>0</v>
@@ -32009,7 +32012,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="467" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A467" s="2"/>
       <c r="B467" s="2" t="b">
         <v>0</v>
@@ -32066,7 +32069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="468" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A468" s="2"/>
       <c r="B468" s="2" t="b">
         <v>0</v>
@@ -32123,7 +32126,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="469" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A469" s="2"/>
       <c r="B469" s="2" t="b">
         <v>0</v>
@@ -32180,7 +32183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="470" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A470" s="2"/>
       <c r="B470" s="2" t="b">
         <v>0</v>
@@ -32237,7 +32240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="471" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A471" s="2"/>
       <c r="B471" s="2" t="b">
         <v>0</v>
@@ -32290,7 +32293,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="472" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A472" s="2"/>
       <c r="B472" s="2" t="b">
         <v>0</v>
@@ -32345,7 +32348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="473" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A473" s="2"/>
       <c r="B473" s="2" t="b">
         <v>0</v>
@@ -32400,7 +32403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="474" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A474" s="2"/>
       <c r="B474" s="2" t="b">
         <v>0</v>
@@ -32455,7 +32458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="475" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A475" s="2"/>
       <c r="B475" s="2" t="b">
         <v>0</v>
@@ -32510,7 +32513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="476" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A476" s="2"/>
       <c r="B476" s="2" t="b">
         <v>0</v>
@@ -32565,7 +32568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="477" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A477" s="2"/>
       <c r="B477" s="2" t="b">
         <v>0</v>
@@ -32620,7 +32623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="478" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A478" s="2"/>
       <c r="B478" s="2" t="b">
         <v>0</v>
@@ -32673,7 +32676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="479" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A479" s="2"/>
       <c r="B479" s="2" t="b">
         <v>0</v>
@@ -32728,7 +32731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="480" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A480" s="2"/>
       <c r="B480" s="2" t="b">
         <v>0</v>
@@ -32783,7 +32786,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="481" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A481" s="2"/>
       <c r="B481" s="2" t="b">
         <v>0</v>
@@ -32838,7 +32841,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="482" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A482" s="2"/>
       <c r="B482" s="2" t="b">
         <v>0</v>
@@ -32893,7 +32896,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="483" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A483" s="2"/>
       <c r="B483" s="2" t="b">
         <v>0</v>
@@ -32948,7 +32951,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="484" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A484" s="2"/>
       <c r="B484" s="2" t="b">
         <v>0</v>
@@ -33003,7 +33006,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="485" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A485" s="2"/>
       <c r="B485" s="2" t="b">
         <v>0</v>
@@ -33058,7 +33061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="486" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A486" s="2"/>
       <c r="B486" s="2" t="b">
         <v>0</v>
@@ -33115,7 +33118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="487" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A487" s="2"/>
       <c r="B487" s="2" t="b">
         <v>0</v>
@@ -33172,7 +33175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="488" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A488" s="2"/>
       <c r="B488" s="2" t="b">
         <v>0</v>
@@ -33229,7 +33232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="489" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A489" s="2"/>
       <c r="B489" s="2" t="b">
         <v>0</v>
@@ -33286,7 +33289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="490" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A490" s="2"/>
       <c r="B490" s="2" t="b">
         <v>0</v>
@@ -33343,7 +33346,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="491" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A491" s="2"/>
       <c r="B491" s="2" t="b">
         <v>0</v>
@@ -33400,7 +33403,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="492" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A492" s="2"/>
       <c r="B492" s="2" t="b">
         <v>0</v>
@@ -33457,7 +33460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="493" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A493" s="2"/>
       <c r="B493" s="2" t="b">
         <v>0</v>
@@ -33514,7 +33517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="494" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A494" s="2"/>
       <c r="B494" s="2" t="b">
         <v>0</v>
@@ -33571,7 +33574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="495" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A495" s="2"/>
       <c r="B495" s="2" t="b">
         <v>0</v>
@@ -33628,7 +33631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="496" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A496" s="2"/>
       <c r="B496" s="2" t="b">
         <v>0</v>
@@ -33685,7 +33688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="497" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A497" s="2"/>
       <c r="B497" s="2" t="b">
         <v>0</v>
@@ -33742,7 +33745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="498" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A498" s="2"/>
       <c r="B498" s="2" t="b">
         <v>0</v>
@@ -33799,7 +33802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="499" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A499" s="2"/>
       <c r="B499" s="2" t="b">
         <v>0</v>
@@ -33856,7 +33859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="500" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A500" s="2"/>
       <c r="B500" s="2" t="b">
         <v>0</v>
@@ -33913,7 +33916,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="501" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A501" s="2"/>
       <c r="B501" s="2" t="b">
         <v>0</v>
@@ -33970,7 +33973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="502" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A502" s="2"/>
       <c r="B502" s="2" t="b">
         <v>0</v>
@@ -34031,7 +34034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="503" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A503" s="2"/>
       <c r="B503" s="2" t="b">
         <v>0</v>
@@ -34092,7 +34095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="504" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A504" s="2"/>
       <c r="B504" s="2" t="b">
         <v>0</v>
@@ -34153,7 +34156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="505" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A505" s="2"/>
       <c r="B505" s="2" t="b">
         <v>0</v>
@@ -34214,7 +34217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="506" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A506" s="2"/>
       <c r="B506" s="2" t="b">
         <v>0</v>
@@ -34275,7 +34278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="507" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A507" s="2"/>
       <c r="B507" s="2" t="b">
         <v>0</v>
@@ -34336,7 +34339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="508" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A508" s="2"/>
       <c r="B508" s="2" t="b">
         <v>0</v>
@@ -34397,7 +34400,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="509" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A509" s="2"/>
       <c r="B509" s="2" t="b">
         <v>0</v>
@@ -34458,7 +34461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="510" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A510" s="2"/>
       <c r="B510" s="2" t="b">
         <v>0</v>
@@ -34519,7 +34522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="511" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A511" s="2"/>
       <c r="B511" s="2" t="b">
         <v>0</v>
@@ -34580,7 +34583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="512" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A512" s="2"/>
       <c r="B512" s="2" t="b">
         <v>0</v>
@@ -34641,7 +34644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="513" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A513" s="2"/>
       <c r="B513" s="2" t="b">
         <v>0</v>
@@ -34702,7 +34705,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="514" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A514" s="2"/>
       <c r="B514" s="2" t="b">
         <v>0</v>
@@ -34763,7 +34766,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="515" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A515" s="2"/>
       <c r="B515" s="2" t="b">
         <v>0</v>
@@ -34824,7 +34827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="516" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A516" s="2"/>
       <c r="B516" s="2" t="b">
         <v>0</v>
@@ -34885,7 +34888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="517" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A517" s="2"/>
       <c r="B517" s="2" t="b">
         <v>0</v>
@@ -34946,7 +34949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="518" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A518" s="2"/>
       <c r="B518" s="2" t="b">
         <v>0</v>
@@ -35007,7 +35010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="519" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A519" s="2"/>
       <c r="B519" s="2" t="b">
         <v>0</v>
@@ -35068,7 +35071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="520" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A520" s="2"/>
       <c r="B520" s="2" t="b">
         <v>0</v>
@@ -35129,7 +35132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="521" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A521" s="2"/>
       <c r="B521" s="2" t="b">
         <v>0</v>
@@ -35190,7 +35193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="522" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A522" s="2"/>
       <c r="B522" s="2" t="b">
         <v>0</v>
@@ -35251,7 +35254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A523" s="2"/>
       <c r="B523" s="2" t="b">
         <v>0</v>
@@ -35312,7 +35315,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="524" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A524" s="2"/>
       <c r="B524" s="2" t="b">
         <v>0</v>
@@ -35373,7 +35376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="525" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A525" s="2"/>
       <c r="B525" s="2" t="b">
         <v>0</v>
@@ -35434,7 +35437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="526" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A526" s="2"/>
       <c r="B526" s="2" t="b">
         <v>0</v>
@@ -35495,7 +35498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="527" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A527" s="2"/>
       <c r="B527" s="2" t="b">
         <v>0</v>
@@ -35556,7 +35559,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="528" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A528" s="2"/>
       <c r="B528" s="2" t="b">
         <v>0</v>
@@ -35617,7 +35620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="529" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A529" s="2"/>
       <c r="B529" s="2" t="b">
         <v>0</v>
@@ -35678,7 +35681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="530" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A530" s="2"/>
       <c r="B530" s="2" t="b">
         <v>0</v>
@@ -35739,7 +35742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="531" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A531" s="2"/>
       <c r="B531" s="2" t="b">
         <v>0</v>
@@ -35800,7 +35803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="532" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A532" s="2"/>
       <c r="B532" s="2" t="b">
         <v>0</v>
@@ -35861,7 +35864,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="533" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A533" s="2"/>
       <c r="B533" s="2" t="b">
         <v>0</v>
@@ -35922,7 +35925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A534" s="2"/>
       <c r="B534" s="2" t="b">
         <v>0</v>
@@ -35983,7 +35986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="535" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A535" s="2"/>
       <c r="B535" s="2" t="b">
         <v>0</v>
@@ -36044,7 +36047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="536" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A536" s="2"/>
       <c r="B536" s="2" t="b">
         <v>0</v>
@@ -36105,7 +36108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="537" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A537" s="2"/>
       <c r="B537" s="2" t="b">
         <v>0</v>
@@ -36166,7 +36169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="538" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A538" s="2"/>
       <c r="B538" s="2" t="b">
         <v>0</v>
@@ -36227,7 +36230,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="539" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A539" s="2"/>
       <c r="B539" s="2" t="b">
         <v>0</v>
@@ -36288,7 +36291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A540" s="2"/>
       <c r="B540" s="2" t="b">
         <v>0</v>
@@ -36349,7 +36352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="541" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A541" s="2"/>
       <c r="B541" s="2" t="b">
         <v>0</v>
@@ -36410,7 +36413,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="542" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A542" s="2"/>
       <c r="B542" s="2" t="b">
         <v>0</v>
@@ -36471,7 +36474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="543" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A543" s="2"/>
       <c r="B543" s="2" t="b">
         <v>0</v>
@@ -36532,7 +36535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="544" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A544" s="2"/>
       <c r="B544" s="2" t="b">
         <v>0</v>
@@ -36593,7 +36596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="545" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A545" s="2"/>
       <c r="B545" s="2" t="b">
         <v>0</v>
@@ -36654,7 +36657,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="546" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A546" s="2"/>
       <c r="B546" s="2" t="b">
         <v>0</v>
@@ -36715,7 +36718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="547" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A547" s="2"/>
       <c r="B547" s="2" t="b">
         <v>0</v>
@@ -36776,7 +36779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A548" s="2"/>
       <c r="B548" s="2" t="b">
         <v>0</v>
@@ -36837,7 +36840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="549" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A549" s="2"/>
       <c r="B549" s="2" t="b">
         <v>0</v>
@@ -36898,7 +36901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="550" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A550" s="2"/>
       <c r="B550" s="2" t="b">
         <v>0</v>
@@ -36959,7 +36962,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="551" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A551" s="2"/>
       <c r="B551" s="2" t="b">
         <v>0</v>
@@ -37020,7 +37023,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="552" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A552" s="2"/>
       <c r="B552" s="2" t="b">
         <v>0</v>
@@ -37081,7 +37084,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="553" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A553" s="2"/>
       <c r="B553" s="2" t="b">
         <v>0</v>
@@ -37142,7 +37145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="554" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A554" s="2"/>
       <c r="B554" s="2" t="b">
         <v>0</v>
@@ -37203,7 +37206,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="555" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A555" s="2"/>
       <c r="B555" s="2" t="b">
         <v>0</v>
@@ -37264,7 +37267,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A556" s="2"/>
       <c r="B556" s="2" t="b">
         <v>0</v>
@@ -37325,7 +37328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="557" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A557" s="2"/>
       <c r="B557" s="2" t="b">
         <v>0</v>
@@ -37374,7 +37377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="558" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A558" s="2"/>
       <c r="B558" s="2" t="b">
         <v>0</v>
@@ -37423,7 +37426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="559" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A559" s="2"/>
       <c r="B559" s="2" t="b">
         <v>0</v>
@@ -37472,7 +37475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="560" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A560" s="2">
         <v>83</v>
       </c>
@@ -37535,7 +37538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="561" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A561" s="2">
         <v>83</v>
       </c>
@@ -37598,7 +37601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A562" s="2">
         <v>83</v>
       </c>
@@ -37661,7 +37664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="563" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A563" s="2"/>
       <c r="B563" s="2" t="b">
         <v>0</v>
@@ -37722,7 +37725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="564" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A564" s="2"/>
       <c r="B564" s="2" t="b">
         <v>1</v>
@@ -37783,7 +37786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="565" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A565" s="2"/>
       <c r="B565" s="2" t="b">
         <v>0</v>
@@ -37844,7 +37847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="566" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A566" s="2">
         <v>85</v>
       </c>
@@ -37907,7 +37910,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="567" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A567" s="2">
         <v>85</v>
       </c>
@@ -37970,7 +37973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="568" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A568" s="2">
         <v>85</v>
       </c>
@@ -38033,7 +38036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="569" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A569" s="2">
         <v>86</v>
       </c>
@@ -38096,7 +38099,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="570" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A570" s="2">
         <v>86</v>
       </c>
@@ -38159,7 +38162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="571" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A571" s="2">
         <v>86</v>
       </c>
@@ -38222,7 +38225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A572" s="2">
         <v>84</v>
       </c>
@@ -38285,7 +38288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A573" s="2">
         <v>84</v>
       </c>
@@ -38348,7 +38351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="574" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A574" s="2">
         <v>84</v>
       </c>
@@ -38411,7 +38414,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A575" s="2"/>
       <c r="B575" s="2" t="b">
         <v>0</v>
@@ -38460,7 +38463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="576" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A576" s="2">
         <v>80</v>
       </c>
@@ -38519,7 +38522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="577" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A577" s="2">
         <v>80</v>
       </c>
@@ -38578,7 +38581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="578" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A578" s="2">
         <v>80</v>
       </c>
@@ -38637,7 +38640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="579" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A579" s="2">
         <v>80</v>
       </c>
@@ -38696,7 +38699,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="580" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A580" s="2">
         <v>80</v>
       </c>
@@ -38755,7 +38758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="581" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A581" s="2">
         <v>80</v>
       </c>
@@ -38814,7 +38817,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="582" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A582" s="2">
         <v>80</v>
       </c>
@@ -38873,7 +38876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="583" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A583" s="2">
         <v>80</v>
       </c>
@@ -38932,7 +38935,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="584" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A584" s="2">
         <v>80</v>
       </c>
@@ -38991,7 +38994,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="585" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A585" s="2"/>
       <c r="B585" s="2" t="b">
         <v>0</v>
@@ -39042,7 +39045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="586" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A586" s="2">
         <v>91</v>
       </c>
@@ -39101,7 +39104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="587" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A587" s="2">
         <v>91</v>
       </c>
@@ -39160,7 +39163,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="588" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A588" s="2">
         <v>91</v>
       </c>
@@ -39219,7 +39222,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="589" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A589" s="2">
         <v>91</v>
       </c>
@@ -39278,7 +39281,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="590" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A590" s="2">
         <v>91</v>
       </c>
@@ -39337,7 +39340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="591" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A591" s="2">
         <v>91</v>
       </c>
@@ -39396,7 +39399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="592" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A592" s="2">
         <v>91</v>
       </c>
@@ -39455,7 +39458,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="593" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A593" s="2"/>
       <c r="B593" s="2" t="b">
         <v>0</v>
@@ -39512,7 +39515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="594" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A594" s="2"/>
       <c r="B594" s="2" t="b">
         <v>0</v>
@@ -39569,7 +39572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="595" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A595" s="2"/>
       <c r="B595" s="2" t="b">
         <v>0</v>
@@ -39626,7 +39629,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="596" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A596" s="2"/>
       <c r="B596" s="2" t="b">
         <v>0</v>
@@ -39683,7 +39686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="597" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A597" s="2"/>
       <c r="B597" s="2" t="b">
         <v>0</v>
@@ -39740,7 +39743,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="598" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A598" s="2"/>
       <c r="B598" s="2" t="b">
         <v>0</v>
@@ -39797,7 +39800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="599" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A599" s="2"/>
       <c r="B599" s="2" t="b">
         <v>0</v>
@@ -39854,7 +39857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="600" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A600" s="2"/>
       <c r="B600" s="2" t="b">
         <v>0</v>
@@ -39911,7 +39914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="601" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A601" s="2"/>
       <c r="B601" s="2" t="b">
         <v>0</v>
@@ -39968,7 +39971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="602" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A602" s="2"/>
       <c r="B602" s="2" t="b">
         <v>0</v>
@@ -40023,7 +40026,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="603" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A603" s="2"/>
       <c r="B603" s="2" t="b">
         <v>0</v>
@@ -40078,7 +40081,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="604" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A604" s="2"/>
       <c r="B604" s="2" t="b">
         <v>0</v>
@@ -40133,7 +40136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="605" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A605" s="2"/>
       <c r="B605" s="2" t="b">
         <v>0</v>
@@ -40188,7 +40191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="606" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A606" s="2"/>
       <c r="B606" s="2" t="b">
         <v>0</v>
@@ -40243,7 +40246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="607" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A607" s="2"/>
       <c r="B607" s="2" t="b">
         <v>0</v>
@@ -40298,7 +40301,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="608" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A608" s="2"/>
       <c r="B608" s="2" t="b">
         <v>0</v>
@@ -40353,7 +40356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="609" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A609" s="2"/>
       <c r="B609" s="2" t="b">
         <v>0</v>
@@ -40408,7 +40411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="610" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A610" s="2"/>
       <c r="B610" s="2" t="b">
         <v>0</v>
@@ -40463,7 +40466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="611" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A611" s="2"/>
       <c r="B611" s="2" t="b">
         <v>0</v>
@@ -40518,7 +40521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="612" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A612" s="2"/>
       <c r="B612" s="2" t="b">
         <v>0</v>
@@ -40571,7 +40574,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="613" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A613" s="2"/>
       <c r="B613" s="2" t="b">
         <v>0</v>
@@ -40624,7 +40627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A614" s="2"/>
       <c r="B614" s="2" t="b">
         <v>0</v>
@@ -40675,7 +40678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="615" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A615" s="2">
         <v>67</v>
       </c>
@@ -40738,7 +40741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="616" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A616" s="2">
         <v>67</v>
       </c>
@@ -40801,7 +40804,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="617" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A617" s="2">
         <v>67</v>
       </c>
@@ -40864,7 +40867,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="618" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A618" s="2">
         <v>67</v>
       </c>
@@ -40927,7 +40930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="619" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A619" s="2">
         <v>67</v>
       </c>
@@ -40990,7 +40993,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="620" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A620" s="2"/>
       <c r="B620" s="2" t="b">
         <v>0</v>
@@ -41047,7 +41050,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="621" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A621" s="2"/>
       <c r="B621" s="2" t="b">
         <v>0</v>
@@ -41104,7 +41107,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="622" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A622" s="2"/>
       <c r="B622" s="2" t="b">
         <v>0</v>
@@ -41161,7 +41164,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="623" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A623" s="2"/>
       <c r="B623" s="2" t="b">
         <v>0</v>
@@ -41218,7 +41221,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="624" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A624" s="2"/>
       <c r="B624" s="2" t="b">
         <v>0</v>
@@ -41275,7 +41278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="625" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A625" s="2"/>
       <c r="B625" s="2" t="b">
         <v>0</v>
@@ -41332,7 +41335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="626" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A626" s="2"/>
       <c r="B626" s="2" t="b">
         <v>0</v>
@@ -41389,7 +41392,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="627" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A627" s="2"/>
       <c r="B627" s="2" t="b">
         <v>0</v>
@@ -41446,7 +41449,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A628" s="2"/>
       <c r="B628" s="2" t="b">
         <v>0</v>
@@ -41503,7 +41506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="629" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A629" s="2"/>
       <c r="B629" s="2" t="b">
         <v>0</v>
@@ -41560,7 +41563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="630" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A630" s="2"/>
       <c r="B630" s="2" t="b">
         <v>0</v>
@@ -41617,7 +41620,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="631" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A631" s="2"/>
       <c r="B631" s="2" t="b">
         <v>0</v>
@@ -41674,7 +41677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A632" s="2"/>
       <c r="B632" s="2" t="b">
         <v>0</v>
@@ -41731,7 +41734,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="633" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A633" s="2"/>
       <c r="B633" s="2" t="b">
         <v>0</v>
@@ -41788,7 +41791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="634" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A634" s="2">
         <v>77</v>
       </c>
@@ -41847,7 +41850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="635" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A635" s="2">
         <v>77</v>
       </c>
@@ -41906,7 +41909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="636" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A636" s="2">
         <v>77</v>
       </c>
@@ -41965,7 +41968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="637" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A637" s="2">
         <v>77</v>
       </c>
@@ -42024,7 +42027,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="638" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A638" s="2">
         <v>77</v>
       </c>
@@ -42083,7 +42086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="639" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A639" s="2"/>
       <c r="B639" s="2" t="b">
         <v>0</v>
@@ -42132,7 +42135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="640" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A640" s="2"/>
       <c r="B640" s="2" t="b">
         <v>0</v>
@@ -42181,7 +42184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="641" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A641" s="2"/>
       <c r="B641" s="2" t="b">
         <v>0</v>
@@ -42238,7 +42241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A642" s="2"/>
       <c r="B642" s="2" t="b">
         <v>0</v>
@@ -42295,7 +42298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="643" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A643" s="2">
         <v>65</v>
       </c>
@@ -42354,7 +42357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="644" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A644" s="2">
         <v>65</v>
       </c>
@@ -42413,7 +42416,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A645" s="2">
         <v>65</v>
       </c>
@@ -42472,7 +42475,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="646" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A646" s="2">
         <v>65</v>
       </c>
@@ -42531,7 +42534,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="647" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A647" s="2">
         <v>65</v>
       </c>
@@ -42590,7 +42593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="648" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A648" s="2">
         <v>65</v>
       </c>
@@ -42649,7 +42652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="649" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A649" s="2"/>
       <c r="B649" s="2" t="b">
         <v>0</v>
@@ -42704,7 +42707,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="650" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A650" s="2"/>
       <c r="B650" s="2" t="b">
         <v>0</v>
@@ -42759,7 +42762,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="651" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A651" s="2">
         <v>68</v>
       </c>
@@ -42816,7 +42819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="652" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A652" s="2">
         <v>68</v>
       </c>
@@ -42873,7 +42876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="653" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A653" s="2">
         <v>69</v>
       </c>
@@ -42914,7 +42917,7 @@
         <v>509</v>
       </c>
       <c r="P653" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q653" s="2"/>
       <c r="R653" s="2" t="s">
@@ -42930,7 +42933,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="654" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A654" s="2">
         <v>69</v>
       </c>
@@ -42971,7 +42974,7 @@
         <v>509</v>
       </c>
       <c r="P654" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q654" s="2"/>
       <c r="R654" s="2" t="s">
@@ -42987,7 +42990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="655" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A655" s="2">
         <v>69</v>
       </c>
@@ -43028,7 +43031,7 @@
         <v>509</v>
       </c>
       <c r="P655" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q655" s="2"/>
       <c r="R655" s="2" t="s">
@@ -43044,7 +43047,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="656" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A656" s="2">
         <v>69</v>
       </c>
@@ -43085,7 +43088,7 @@
         <v>509</v>
       </c>
       <c r="P656" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q656" s="2"/>
       <c r="R656" s="2" t="s">
@@ -43101,7 +43104,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="657" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A657" s="2">
         <v>69</v>
       </c>
@@ -43142,7 +43145,7 @@
         <v>509</v>
       </c>
       <c r="P657" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q657" s="2"/>
       <c r="R657" s="2" t="s">
@@ -43158,7 +43161,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="658" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A658" s="2">
         <v>69</v>
       </c>
@@ -43199,7 +43202,7 @@
         <v>509</v>
       </c>
       <c r="P658" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q658" s="2"/>
       <c r="R658" s="2" t="s">
@@ -43215,7 +43218,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="659" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A659" s="2">
         <v>69</v>
       </c>
@@ -43256,7 +43259,7 @@
         <v>509</v>
       </c>
       <c r="P659" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q659" s="2"/>
       <c r="R659" s="2" t="s">
@@ -43272,7 +43275,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="660" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A660" s="2">
         <v>70</v>
       </c>
@@ -43317,7 +43320,7 @@
         <v>15</v>
       </c>
       <c r="P660" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q660" s="2"/>
       <c r="R660" s="2" t="s">
@@ -43333,7 +43336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="661" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A661" s="2">
         <v>70</v>
       </c>
@@ -43378,7 +43381,7 @@
         <v>15</v>
       </c>
       <c r="P661" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q661" s="2"/>
       <c r="R661" s="2" t="s">
@@ -43394,7 +43397,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="662" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A662" s="2">
         <v>70</v>
       </c>
@@ -43439,7 +43442,7 @@
         <v>15</v>
       </c>
       <c r="P662" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q662" s="2"/>
       <c r="R662" s="2" t="s">
@@ -43455,7 +43458,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="663" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A663" s="2">
         <v>70</v>
       </c>
@@ -43500,7 +43503,7 @@
         <v>15</v>
       </c>
       <c r="P663" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q663" s="2"/>
       <c r="R663" s="2" t="s">
@@ -43516,7 +43519,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="664" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A664" s="2">
         <v>70</v>
       </c>
@@ -43561,7 +43564,7 @@
         <v>15</v>
       </c>
       <c r="P664" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q664" s="2"/>
       <c r="R664" s="2" t="s">
@@ -43577,7 +43580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="665" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A665" s="2">
         <v>66</v>
       </c>
@@ -43622,7 +43625,7 @@
         <v>15</v>
       </c>
       <c r="P665" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q665" s="2"/>
       <c r="R665" s="2" t="s">
@@ -43638,7 +43641,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="666" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A666" s="2">
         <v>66</v>
       </c>
@@ -43683,7 +43686,7 @@
         <v>15</v>
       </c>
       <c r="P666" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q666" s="2"/>
       <c r="R666" s="2" t="s">
@@ -43699,7 +43702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="667" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A667" s="2">
         <v>66</v>
       </c>
@@ -43744,7 +43747,7 @@
         <v>15</v>
       </c>
       <c r="P667" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q667" s="2"/>
       <c r="R667" s="2" t="s">
@@ -43760,7 +43763,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="668" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A668" s="2">
         <v>66</v>
       </c>
@@ -43805,7 +43808,7 @@
         <v>15</v>
       </c>
       <c r="P668" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q668" s="2"/>
       <c r="R668" s="2" t="s">
@@ -43821,7 +43824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="669" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A669" s="2">
         <v>66</v>
       </c>
@@ -43866,7 +43869,7 @@
         <v>15</v>
       </c>
       <c r="P669" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q669" s="2"/>
       <c r="R669" s="2" t="s">
@@ -43882,7 +43885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="670" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A670" s="2">
         <v>71</v>
       </c>
@@ -43927,7 +43930,7 @@
         <v>15</v>
       </c>
       <c r="P670" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q670" s="2"/>
       <c r="R670" s="2" t="s">
@@ -43943,7 +43946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="671" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A671" s="2">
         <v>71</v>
       </c>
@@ -43988,7 +43991,7 @@
         <v>15</v>
       </c>
       <c r="P671" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q671" s="2"/>
       <c r="R671" s="2" t="s">
@@ -44004,7 +44007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="672" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A672" s="2">
         <v>71</v>
       </c>
@@ -44049,7 +44052,7 @@
         <v>15</v>
       </c>
       <c r="P672" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q672" s="2"/>
       <c r="R672" s="2" t="s">
@@ -44065,7 +44068,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="673" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A673" s="2">
         <v>71</v>
       </c>
@@ -44110,7 +44113,7 @@
         <v>15</v>
       </c>
       <c r="P673" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q673" s="2"/>
       <c r="R673" s="2" t="s">
@@ -44126,7 +44129,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="674" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A674" s="2">
         <v>71</v>
       </c>
@@ -44171,7 +44174,7 @@
         <v>15</v>
       </c>
       <c r="P674" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q674" s="2"/>
       <c r="R674" s="2" t="s">
@@ -44187,7 +44190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="675" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A675" s="2">
         <v>72</v>
       </c>
@@ -44232,7 +44235,7 @@
         <v>15</v>
       </c>
       <c r="P675" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q675" s="2"/>
       <c r="R675" s="2" t="s">
@@ -44248,7 +44251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="676" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A676" s="2">
         <v>72</v>
       </c>
@@ -44293,7 +44296,7 @@
         <v>15</v>
       </c>
       <c r="P676" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q676" s="2"/>
       <c r="R676" s="2" t="s">
@@ -44309,7 +44312,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="677" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A677" s="2">
         <v>72</v>
       </c>
@@ -44354,7 +44357,7 @@
         <v>15</v>
       </c>
       <c r="P677" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q677" s="2"/>
       <c r="R677" s="2" t="s">
@@ -44370,7 +44373,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="678" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A678" s="2">
         <v>72</v>
       </c>
@@ -44415,7 +44418,7 @@
         <v>15</v>
       </c>
       <c r="P678" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q678" s="2"/>
       <c r="R678" s="2" t="s">
@@ -44431,7 +44434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="679" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A679" s="2">
         <v>72</v>
       </c>
@@ -44476,7 +44479,7 @@
         <v>15</v>
       </c>
       <c r="P679" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q679" s="2"/>
       <c r="R679" s="2" t="s">
@@ -44492,7 +44495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="680" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A680" s="2">
         <v>73</v>
       </c>
@@ -44537,7 +44540,7 @@
         <v>15</v>
       </c>
       <c r="P680" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q680" s="2"/>
       <c r="R680" s="2" t="s">
@@ -44553,7 +44556,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="681" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A681" s="2">
         <v>73</v>
       </c>
@@ -44598,7 +44601,7 @@
         <v>15</v>
       </c>
       <c r="P681" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q681" s="2"/>
       <c r="R681" s="2" t="s">
@@ -44614,7 +44617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="682" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A682" s="2">
         <v>73</v>
       </c>
@@ -44659,7 +44662,7 @@
         <v>15</v>
       </c>
       <c r="P682" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q682" s="2"/>
       <c r="R682" s="2" t="s">
@@ -44675,7 +44678,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="683" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A683" s="2">
         <v>73</v>
       </c>
@@ -44720,7 +44723,7 @@
         <v>15</v>
       </c>
       <c r="P683" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q683" s="2"/>
       <c r="R683" s="2" t="s">
@@ -44736,7 +44739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="684" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A684" s="2">
         <v>73</v>
       </c>
@@ -44781,7 +44784,7 @@
         <v>15</v>
       </c>
       <c r="P684" s="2" t="s">
-        <v>521</v>
+        <v>743</v>
       </c>
       <c r="Q684" s="2"/>
       <c r="R684" s="2" t="s">
@@ -44797,7 +44800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="685" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A685" s="2"/>
       <c r="B685" s="2" t="b">
         <v>0</v>
@@ -44856,7 +44859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="686" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A686" s="2"/>
       <c r="B686" s="2" t="b">
         <v>0</v>
@@ -44915,7 +44918,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="687" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A687" s="2"/>
       <c r="B687" s="2" t="b">
         <v>0</v>
@@ -44974,7 +44977,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="688" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A688" s="2"/>
       <c r="B688" s="2" t="b">
         <v>0</v>
@@ -45033,7 +45036,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="689" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A689" s="2"/>
       <c r="B689" s="2" t="b">
         <v>0</v>
@@ -45092,7 +45095,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="690" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A690" s="2"/>
       <c r="B690" s="2" t="b">
         <v>0</v>
@@ -45151,7 +45154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="691" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A691" s="2"/>
       <c r="B691" s="2" t="b">
         <v>0</v>
@@ -45210,7 +45213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="692" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A692" s="2"/>
       <c r="B692" s="2" t="b">
         <v>0</v>
@@ -45269,7 +45272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="693" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A693" s="2"/>
       <c r="B693" s="2" t="b">
         <v>0</v>
@@ -45328,7 +45331,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="694" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A694" s="2"/>
       <c r="B694" s="2" t="b">
         <v>0</v>
@@ -45387,7 +45390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="695" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A695" s="2"/>
       <c r="B695" s="2" t="b">
         <v>0</v>
@@ -45446,7 +45449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="696" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A696" s="2"/>
       <c r="B696" s="2" t="b">
         <v>0</v>
@@ -45505,7 +45508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="697" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A697" s="2"/>
       <c r="B697" s="2" t="b">
         <v>0</v>
@@ -45564,7 +45567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="698" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A698" s="2"/>
       <c r="B698" s="2" t="b">
         <v>0</v>
@@ -45623,7 +45626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="699" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A699" s="2"/>
       <c r="B699" s="2" t="b">
         <v>0</v>
@@ -45682,7 +45685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="700" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A700" s="2"/>
       <c r="B700" s="2" t="b">
         <v>0</v>
@@ -45741,7 +45744,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="701" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A701" s="2"/>
       <c r="B701" s="2" t="b">
         <v>0</v>
@@ -45800,7 +45803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="702" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A702" s="2"/>
       <c r="B702" s="2" t="b">
         <v>0</v>
@@ -45859,7 +45862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="703" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A703" s="2"/>
       <c r="B703" s="2" t="b">
         <v>0</v>
@@ -45918,7 +45921,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="704" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A704" s="2"/>
       <c r="B704" s="2" t="b">
         <v>0</v>
@@ -45977,7 +45980,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="705" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A705" s="2"/>
       <c r="B705" s="2" t="b">
         <v>0</v>
@@ -46036,7 +46039,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="706" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A706" s="2"/>
       <c r="B706" s="2" t="b">
         <v>0</v>
@@ -46095,7 +46098,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="707" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A707" s="2"/>
       <c r="B707" s="2" t="b">
         <v>0</v>
@@ -46154,7 +46157,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="708" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A708" s="2"/>
       <c r="B708" s="2" t="b">
         <v>0</v>
@@ -46213,7 +46216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="709" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A709" s="2"/>
       <c r="B709" s="2" t="b">
         <v>0</v>
@@ -46272,7 +46275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="710" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A710" s="2"/>
       <c r="B710" s="2" t="b">
         <v>0</v>
@@ -46331,7 +46334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="711" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A711" s="2"/>
       <c r="B711" s="2" t="b">
         <v>0</v>
@@ -46390,7 +46393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="712" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A712" s="2"/>
       <c r="B712" s="2" t="b">
         <v>0</v>
@@ -46449,7 +46452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="713" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A713" s="2"/>
       <c r="B713" s="2" t="b">
         <v>0</v>
@@ -46508,7 +46511,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="714" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A714" s="2"/>
       <c r="B714" s="2" t="b">
         <v>0</v>
@@ -46567,7 +46570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="715" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A715" s="2"/>
       <c r="B715" s="2" t="b">
         <v>0</v>
@@ -46626,7 +46629,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="716" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A716" s="2"/>
       <c r="B716" s="2" t="b">
         <v>0</v>
@@ -46685,7 +46688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="717" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A717" s="2"/>
       <c r="B717" s="2" t="b">
         <v>0</v>
@@ -46744,7 +46747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="718" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A718" s="2"/>
       <c r="B718" s="2" t="b">
         <v>0</v>
@@ -46803,7 +46806,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="719" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A719" s="2"/>
       <c r="B719" s="2" t="b">
         <v>0</v>
@@ -46862,7 +46865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="720" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A720" s="2"/>
       <c r="B720" s="2" t="b">
         <v>0</v>
@@ -46921,7 +46924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="721" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A721" s="2"/>
       <c r="B721" s="2" t="b">
         <v>0</v>
@@ -46980,7 +46983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="722" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A722" s="2"/>
       <c r="B722" s="2" t="b">
         <v>0</v>
@@ -47039,7 +47042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="723" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A723" s="2"/>
       <c r="B723" s="2" t="b">
         <v>0</v>
@@ -47098,7 +47101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="724" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A724" s="2"/>
       <c r="B724" s="2" t="b">
         <v>0</v>
@@ -47157,7 +47160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="725" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A725" s="2"/>
       <c r="B725" s="2" t="b">
         <v>0</v>
@@ -47216,7 +47219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="726" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A726" s="2"/>
       <c r="B726" s="2" t="b">
         <v>0</v>
@@ -47275,7 +47278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="727" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A727" s="2"/>
       <c r="B727" s="2" t="b">
         <v>0</v>
@@ -47334,7 +47337,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="728" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A728" s="2"/>
       <c r="B728" s="2" t="b">
         <v>0</v>
@@ -47393,7 +47396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="729" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A729" s="2"/>
       <c r="B729" s="2" t="b">
         <v>0</v>
@@ -47448,7 +47451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="730" spans="1:21" ht="18" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:21" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A730" s="2"/>
       <c r="B730" s="2" t="b">
         <v>0</v>
@@ -47509,77 +47512,77 @@
     <sortCondition ref="A2:A642"/>
   </sortState>
   <conditionalFormatting sqref="A1:T1 T1:U730 A2:F305 I653:J653 G660:J730">
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="14" priority="5">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D665:E684">
-    <cfRule type="expression" dxfId="13" priority="42">
+    <cfRule type="expression" dxfId="13" priority="43">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D306:F652">
-    <cfRule type="expression" dxfId="12" priority="3">
+    <cfRule type="expression" dxfId="12" priority="4">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G671:G674">
-    <cfRule type="expression" dxfId="11" priority="41">
+    <cfRule type="expression" dxfId="11" priority="42">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:J652">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H675">
-    <cfRule type="expression" dxfId="9" priority="39">
+    <cfRule type="expression" dxfId="9" priority="40">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H680">
-    <cfRule type="expression" dxfId="8" priority="36">
+    <cfRule type="expression" dxfId="8" priority="37">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I670:I673">
-    <cfRule type="expression" dxfId="7" priority="35">
+    <cfRule type="expression" dxfId="7" priority="36">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I675:I678">
-    <cfRule type="expression" dxfId="6" priority="34">
+    <cfRule type="expression" dxfId="6" priority="35">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I680:I683">
-    <cfRule type="expression" dxfId="5" priority="33">
+    <cfRule type="expression" dxfId="5" priority="34">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K730">
-    <cfRule type="expression" dxfId="4" priority="5">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:P303 S256:T301 Q294:R303 S302:S303 T302:T305 L304:S305 A306:B489 Q306:R565 L306:P626 S306:T642 C306:C730 A493:B730 D653:H660 G659:I659 D661:F730">
-    <cfRule type="expression" dxfId="3" priority="27">
+    <cfRule type="expression" dxfId="3" priority="28">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:T2 Q3:T255 Q256:R287 Q566:Q628 R566:R642 M629:Q630 L631:Q642 L643:T650 M651:T652 R653:T693 L694:N730 Q694:T730">
-    <cfRule type="expression" dxfId="2" priority="44">
+    <cfRule type="expression" dxfId="2" priority="45">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P653:Q685">
-    <cfRule type="expression" dxfId="1" priority="20">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q288:Q291 R288:R293 Q293 B490:B491 A490:A492 M627:P628 L627:L630 L651:L693 M653:O653 O653:O730 I654:I658 J654:J659 M654:N693 Q686:Q693 P686:P730">
-    <cfRule type="expression" dxfId="0" priority="46">
+    <cfRule type="expression" dxfId="0" priority="47">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
   </conditionalFormatting>
